--- a/mlb_weather_professional_v5_2026_08_08.xlsx
+++ b/mlb_weather_professional_v5_2026_08_08.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="396">
   <si>
     <t>Date</t>
   </si>
@@ -578,7 +578,19 @@
     <t>🟨 Neutral</t>
   </si>
   <si>
-    <t>FIRST RUN</t>
+    <t>IMPROVING RAPIDLY</t>
+  </si>
+  <si>
+    <t>IMPROVING</t>
+  </si>
+  <si>
+    <t>STEADY</t>
+  </si>
+  <si>
+    <t>WORSENING</t>
+  </si>
+  <si>
+    <t>WORSENING RAPIDLY</t>
   </si>
   <si>
     <t>MODERATE</t>
@@ -593,49 +605,46 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-08-08 08:02:09 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:10 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:12 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:13 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:14 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:15 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:17 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:18 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:19 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:21 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:22 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:23 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:24 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:26 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:02:27 AM PDT</t>
+    <t>2026-08-08 08:03:37 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:38 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:39 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:40 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:41 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:42 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:43 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:44 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:45 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:46 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:47 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:48 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:49 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:03:50 AM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1022,49 +1031,46 @@
     <t>09:50 PM PDT</t>
   </si>
   <si>
-    <t>2026-08-08 15:02:09 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:10 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:12 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:13 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:14 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:15 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:17 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:18 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:19 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:21 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:22 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:23 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:02:27 UTC</t>
+    <t>2026-08-08 15:03:37 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:38 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:39 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:40 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:41 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:42 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:43 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:44 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:45 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:46 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:47 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:48 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:49 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:03:50 UTC</t>
   </si>
   <si>
     <t>2026-08-08T06:28:19+00:00</t>
@@ -1687,7 +1693,7 @@
     <col min="40" max="40" width="22.7109375" customWidth="1"/>
     <col min="41" max="41" width="17.7109375" customWidth="1"/>
     <col min="42" max="42" width="15.7109375" customWidth="1"/>
-    <col min="43" max="43" width="16.7109375" customWidth="1"/>
+    <col min="43" max="43" width="19.7109375" customWidth="1"/>
     <col min="44" max="44" width="34.7109375" customWidth="1"/>
     <col min="45" max="45" width="33.7109375" customWidth="1"/>
     <col min="46" max="46" width="32.7109375" customWidth="1"/>
@@ -1987,7 +1993,7 @@
         <v>185</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="AS2">
         <v>0</v>
@@ -1996,22 +2002,22 @@
         <v>9</v>
       </c>
       <c r="AU2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AV2">
         <v>26.3</v>
       </c>
       <c r="AW2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX2">
         <v>5.8</v>
       </c>
       <c r="AY2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AZ2">
-        <v>513.8</v>
+        <v>515.3</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2145,7 +2151,7 @@
         <v>185</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS3">
         <v>-0.17</v>
@@ -2154,22 +2160,22 @@
         <v>13</v>
       </c>
       <c r="AU3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV3">
         <v>18.1</v>
       </c>
       <c r="AW3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX3">
         <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AZ3">
-        <v>41.8</v>
+        <v>43.3</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2300,10 +2306,10 @@
         <v>71.09999999999999</v>
       </c>
       <c r="AQ4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS4">
         <v>-0.14</v>
@@ -2312,22 +2318,22 @@
         <v>10</v>
       </c>
       <c r="AU4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AV4">
         <v>20.7</v>
       </c>
       <c r="AW4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX4">
         <v>6.6</v>
       </c>
       <c r="AY4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AZ4">
-        <v>405.2</v>
+        <v>406.6</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2461,7 +2467,7 @@
         <v>185</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AS5">
         <v>-0.08</v>
@@ -2470,22 +2476,22 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AV5">
         <v>30.8</v>
       </c>
       <c r="AW5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AX5">
         <v>21.7</v>
       </c>
       <c r="AY5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AZ5">
-        <v>413.6</v>
+        <v>415.1</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2616,7 +2622,7 @@
         <v>73.8</v>
       </c>
       <c r="AQ6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2628,22 +2634,22 @@
         <v>10</v>
       </c>
       <c r="AU6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AV6">
         <v>35.6</v>
       </c>
       <c r="AW6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX6">
         <v>16.4</v>
       </c>
       <c r="AY6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AZ6">
-        <v>110.7</v>
+        <v>112.1</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2777,7 +2783,7 @@
         <v>185</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS7">
         <v>0.5</v>
@@ -2786,22 +2792,22 @@
         <v>10</v>
       </c>
       <c r="AU7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AV7">
         <v>22.7</v>
       </c>
       <c r="AW7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX7">
         <v>8.800000000000001</v>
       </c>
       <c r="AY7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AZ7">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -2932,10 +2938,10 @@
         <v>58.2</v>
       </c>
       <c r="AQ8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="AS8">
         <v>-0.22</v>
@@ -2944,22 +2950,22 @@
         <v>10</v>
       </c>
       <c r="AU8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV8">
         <v>13.4</v>
       </c>
       <c r="AW8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX8">
         <v>5.1</v>
       </c>
       <c r="AY8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AZ8">
-        <v>460.6</v>
+        <v>462</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3090,10 +3096,10 @@
         <v>46.3</v>
       </c>
       <c r="AQ9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AS9">
         <v>-0.19</v>
@@ -3102,22 +3108,22 @@
         <v>14</v>
       </c>
       <c r="AU9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV9">
         <v>0.3</v>
       </c>
       <c r="AW9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX9">
         <v>7.4</v>
       </c>
       <c r="AY9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AZ9">
-        <v>30.5</v>
+        <v>31.9</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3248,10 +3254,10 @@
         <v>68.3</v>
       </c>
       <c r="AQ10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="AS10">
         <v>-0.31</v>
@@ -3260,22 +3266,22 @@
         <v>10</v>
       </c>
       <c r="AU10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV10">
         <v>0.2</v>
       </c>
       <c r="AW10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX10">
         <v>14.2</v>
       </c>
       <c r="AY10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AZ10">
-        <v>485.3</v>
+        <v>486.7</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3406,10 +3412,10 @@
         <v>81.7</v>
       </c>
       <c r="AQ11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS11">
         <v>-0.46</v>
@@ -3418,22 +3424,22 @@
         <v>10</v>
       </c>
       <c r="AU11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV11">
         <v>0.5</v>
       </c>
       <c r="AW11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX11">
         <v>16.9</v>
       </c>
       <c r="AY11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AZ11">
-        <v>370.2</v>
+        <v>371.6</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3564,10 +3570,10 @@
         <v>63.4</v>
       </c>
       <c r="AQ12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="AS12">
         <v>-0.98</v>
@@ -3576,22 +3582,22 @@
         <v>12</v>
       </c>
       <c r="AU12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV12">
         <v>12.8</v>
       </c>
       <c r="AW12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX12">
         <v>5.7</v>
       </c>
       <c r="AY12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AZ12">
-        <v>205.9</v>
+        <v>207.3</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3722,10 +3728,10 @@
         <v>33.7</v>
       </c>
       <c r="AQ13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AS13">
         <v>0.14</v>
@@ -3734,22 +3740,22 @@
         <v>14</v>
       </c>
       <c r="AU13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AV13">
         <v>0</v>
       </c>
       <c r="AW13" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX13">
         <v>10.5</v>
       </c>
       <c r="AY13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AZ13">
-        <v>125.3</v>
+        <v>126.7</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3880,10 +3886,10 @@
         <v>66.7</v>
       </c>
       <c r="AQ14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>-6.2</v>
       </c>
       <c r="AS14">
         <v>-0.12</v>
@@ -3892,22 +3898,22 @@
         <v>11</v>
       </c>
       <c r="AU14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV14">
         <v>4.4</v>
       </c>
       <c r="AW14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX14">
         <v>7.9</v>
       </c>
       <c r="AY14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AZ14">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4038,10 +4044,10 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AS15">
         <v>0.08</v>
@@ -4050,22 +4056,22 @@
         <v>11</v>
       </c>
       <c r="AU15" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AV15">
         <v>0</v>
       </c>
       <c r="AW15" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AX15">
         <v>26</v>
       </c>
       <c r="AY15" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AZ15">
-        <v>429.9</v>
+        <v>431.2</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4196,10 +4202,10 @@
         <v>48.2</v>
       </c>
       <c r="AQ16" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>-4.9</v>
       </c>
       <c r="AS16">
         <v>0.48</v>
@@ -4208,22 +4214,22 @@
         <v>13</v>
       </c>
       <c r="AU16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AV16">
         <v>0</v>
       </c>
       <c r="AW16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AX16">
         <v>9.4</v>
       </c>
       <c r="AY16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AZ16">
-        <v>436.5</v>
+        <v>437.9</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4363,286 +4369,286 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="CU1" s="1" t="s">
         <v>49</v>
@@ -4651,16 +4657,16 @@
         <v>48</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:104">
@@ -4677,22 +4683,22 @@
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
         <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J2">
-        <v>513.8</v>
+        <v>515.3</v>
       </c>
       <c r="K2">
         <v>4</v>
@@ -4722,13 +4728,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="V2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="W2">
         <v>0.0833</v>
@@ -4818,10 +4824,10 @@
         <v>230.7</v>
       </c>
       <c r="AZ2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB2">
         <v>94.40000000000001</v>
@@ -4908,7 +4914,7 @@
         <v>1.1422</v>
       </c>
       <c r="CD2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE2">
         <v>2124</v>
@@ -4956,13 +4962,13 @@
         <v>19.4</v>
       </c>
       <c r="CT2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU2">
         <v>5.8</v>
       </c>
       <c r="CV2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW2">
         <v>89</v>
@@ -4991,22 +4997,22 @@
         <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J3">
-        <v>513.8</v>
+        <v>515.3</v>
       </c>
       <c r="K3">
         <v>5</v>
@@ -5036,13 +5042,13 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="V3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="W3">
         <v>0.0833</v>
@@ -5132,10 +5138,10 @@
         <v>233.6</v>
       </c>
       <c r="AZ3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB3">
         <v>93.09999999999999</v>
@@ -5222,7 +5228,7 @@
         <v>1.1412</v>
       </c>
       <c r="CD3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE3">
         <v>2162</v>
@@ -5270,13 +5276,13 @@
         <v>20.7</v>
       </c>
       <c r="CT3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU3">
         <v>2.6</v>
       </c>
       <c r="CV3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW3">
         <v>90</v>
@@ -5305,22 +5311,22 @@
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J4">
-        <v>513.8</v>
+        <v>515.3</v>
       </c>
       <c r="K4">
         <v>6</v>
@@ -5350,13 +5356,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="W4">
         <v>0.0833</v>
@@ -5446,10 +5452,10 @@
         <v>236.3</v>
       </c>
       <c r="AZ4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB4">
         <v>93.2</v>
@@ -5536,7 +5542,7 @@
         <v>1.143</v>
       </c>
       <c r="CD4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE4">
         <v>2116</v>
@@ -5584,13 +5590,13 @@
         <v>24.4</v>
       </c>
       <c r="CT4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU4">
         <v>2.6</v>
       </c>
       <c r="CV4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW4">
         <v>89</v>
@@ -5619,22 +5625,22 @@
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F5" t="s">
         <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J5">
-        <v>513.8</v>
+        <v>515.3</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -5664,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W5">
         <v>0.0833</v>
@@ -5697,7 +5703,7 @@
         <v>0.9</v>
       </c>
       <c r="AE5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AF5">
         <v>89.09999999999999</v>
@@ -5760,10 +5766,10 @@
         <v>241</v>
       </c>
       <c r="AZ5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB5">
         <v>92</v>
@@ -5850,7 +5856,7 @@
         <v>1.1442</v>
       </c>
       <c r="CD5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE5">
         <v>2067</v>
@@ -5898,13 +5904,13 @@
         <v>26.3</v>
       </c>
       <c r="CT5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU5">
         <v>4.4</v>
       </c>
       <c r="CV5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW5">
         <v>88</v>
@@ -5933,22 +5939,22 @@
         <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F6" t="s">
         <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J6">
-        <v>41.8</v>
+        <v>43.3</v>
       </c>
       <c r="K6">
         <v>5.1</v>
@@ -5978,13 +5984,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="V6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="W6">
         <v>0.1667</v>
@@ -6074,10 +6080,10 @@
         <v>257.9</v>
       </c>
       <c r="AZ6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB6">
         <v>95.2</v>
@@ -6164,7 +6170,7 @@
         <v>1.1413</v>
       </c>
       <c r="CD6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE6">
         <v>2172</v>
@@ -6212,13 +6218,13 @@
         <v>15.8</v>
       </c>
       <c r="CT6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU6">
         <v>7.7</v>
       </c>
       <c r="CV6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW6">
         <v>88</v>
@@ -6247,22 +6253,22 @@
         <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G7" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J7">
-        <v>41.8</v>
+        <v>43.3</v>
       </c>
       <c r="K7">
         <v>6.1</v>
@@ -6292,13 +6298,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="W7">
         <v>0.1667</v>
@@ -6388,10 +6394,10 @@
         <v>258.7</v>
       </c>
       <c r="AZ7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB7">
         <v>94.90000000000001</v>
@@ -6478,7 +6484,7 @@
         <v>1.1427</v>
       </c>
       <c r="CD7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE7">
         <v>2126</v>
@@ -6526,13 +6532,13 @@
         <v>16.8</v>
       </c>
       <c r="CT7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU7">
         <v>8.5</v>
       </c>
       <c r="CV7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW7">
         <v>87</v>
@@ -6561,22 +6567,22 @@
         <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G8" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J8">
-        <v>41.8</v>
+        <v>43.3</v>
       </c>
       <c r="K8">
         <v>7.1</v>
@@ -6606,13 +6612,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V8" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W8">
         <v>0.1667</v>
@@ -6702,10 +6708,10 @@
         <v>258.6</v>
       </c>
       <c r="AZ8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB8">
         <v>95.2</v>
@@ -6792,7 +6798,7 @@
         <v>1.145</v>
       </c>
       <c r="CD8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE8">
         <v>2048</v>
@@ -6840,13 +6846,13 @@
         <v>17.1</v>
       </c>
       <c r="CT8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU8">
         <v>7.6</v>
       </c>
       <c r="CV8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW8">
         <v>86</v>
@@ -6875,22 +6881,22 @@
         <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F9" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J9">
-        <v>41.8</v>
+        <v>43.3</v>
       </c>
       <c r="K9">
         <v>8.1</v>
@@ -6920,13 +6926,13 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W9">
         <v>0.1667</v>
@@ -7016,10 +7022,10 @@
         <v>257.8</v>
       </c>
       <c r="AZ9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB9">
         <v>96</v>
@@ -7106,7 +7112,7 @@
         <v>1.1489</v>
       </c>
       <c r="CD9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE9">
         <v>1933</v>
@@ -7154,13 +7160,13 @@
         <v>18.1</v>
       </c>
       <c r="CT9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU9">
         <v>9.800000000000001</v>
       </c>
       <c r="CV9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW9">
         <v>85</v>
@@ -7189,22 +7195,22 @@
         <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F10" t="s">
         <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J10">
-        <v>405.2</v>
+        <v>406.6</v>
       </c>
       <c r="K10">
         <v>5.1</v>
@@ -7234,13 +7240,13 @@
         <v>100</v>
       </c>
       <c r="T10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="V10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="W10">
         <v>0.1667</v>
@@ -7330,10 +7336,10 @@
         <v>103.5</v>
       </c>
       <c r="AZ10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB10">
         <v>97.09999999999999</v>
@@ -7420,7 +7426,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE10">
         <v>858</v>
@@ -7468,13 +7474,13 @@
         <v>0</v>
       </c>
       <c r="CT10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU10">
         <v>4.7</v>
       </c>
       <c r="CV10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW10">
         <v>89</v>
@@ -7503,22 +7509,22 @@
         <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J11">
-        <v>405.2</v>
+        <v>406.6</v>
       </c>
       <c r="K11">
         <v>6.1</v>
@@ -7548,13 +7554,13 @@
         <v>100</v>
       </c>
       <c r="T11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="W11">
         <v>0.1667</v>
@@ -7644,10 +7650,10 @@
         <v>104</v>
       </c>
       <c r="AZ11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB11">
         <v>96.59999999999999</v>
@@ -7734,7 +7740,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE11">
         <v>858</v>
@@ -7782,13 +7788,13 @@
         <v>0</v>
       </c>
       <c r="CT11" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU11">
         <v>5.5</v>
       </c>
       <c r="CV11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW11">
         <v>88</v>
@@ -7817,22 +7823,22 @@
         <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G12" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J12">
-        <v>405.2</v>
+        <v>406.6</v>
       </c>
       <c r="K12">
         <v>7.1</v>
@@ -7862,13 +7868,13 @@
         <v>100</v>
       </c>
       <c r="T12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V12" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W12">
         <v>0.1667</v>
@@ -7952,16 +7958,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AY12">
         <v>100.1</v>
       </c>
       <c r="AZ12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB12">
         <v>96.2</v>
@@ -8048,7 +8054,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD12" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE12">
         <v>858</v>
@@ -8096,13 +8102,13 @@
         <v>0</v>
       </c>
       <c r="CT12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU12">
         <v>6</v>
       </c>
       <c r="CV12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW12">
         <v>87</v>
@@ -8131,22 +8137,22 @@
         <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G13" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J13">
-        <v>405.2</v>
+        <v>406.6</v>
       </c>
       <c r="K13">
         <v>8.1</v>
@@ -8176,13 +8182,13 @@
         <v>100</v>
       </c>
       <c r="T13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W13">
         <v>0.1667</v>
@@ -8266,16 +8272,16 @@
         <v>4.9</v>
       </c>
       <c r="AX13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AY13">
         <v>96.90000000000001</v>
       </c>
       <c r="AZ13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB13">
         <v>95.7</v>
@@ -8362,7 +8368,7 @@
         <v>1.1582</v>
       </c>
       <c r="CD13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE13">
         <v>1562</v>
@@ -8410,13 +8416,13 @@
         <v>20.7</v>
       </c>
       <c r="CT13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU13">
         <v>6.6</v>
       </c>
       <c r="CV13" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW13">
         <v>86</v>
@@ -8445,22 +8451,22 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F14" t="s">
         <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J14">
-        <v>413.6</v>
+        <v>415.1</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -8490,13 +8496,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W14">
         <v>0.0833</v>
@@ -8586,10 +8592,10 @@
         <v>256.2</v>
       </c>
       <c r="AZ14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BA14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BB14">
         <v>88.2</v>
@@ -8676,7 +8682,7 @@
         <v>1.1434</v>
       </c>
       <c r="CD14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE14">
         <v>2082</v>
@@ -8724,13 +8730,13 @@
         <v>30.8</v>
       </c>
       <c r="CT14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU14">
         <v>12.8</v>
       </c>
       <c r="CV14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW14">
         <v>90</v>
@@ -8759,22 +8765,22 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F15" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H15" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J15">
-        <v>413.6</v>
+        <v>415.1</v>
       </c>
       <c r="K15">
         <v>8</v>
@@ -8804,13 +8810,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W15">
         <v>0.0833</v>
@@ -8837,7 +8843,7 @@
         <v>1.6</v>
       </c>
       <c r="AE15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AF15">
         <v>88.59999999999999</v>
@@ -8900,10 +8906,10 @@
         <v>241.7</v>
       </c>
       <c r="AZ15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BA15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BB15">
         <v>89.5</v>
@@ -8990,7 +8996,7 @@
         <v>1.1464</v>
       </c>
       <c r="CD15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE15">
         <v>1992</v>
@@ -9038,13 +9044,13 @@
         <v>28.6</v>
       </c>
       <c r="CT15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU15">
         <v>16.9</v>
       </c>
       <c r="CV15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW15">
         <v>89</v>
@@ -9073,22 +9079,22 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F16" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G16" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H16" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I16" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J16">
-        <v>413.6</v>
+        <v>415.1</v>
       </c>
       <c r="K16">
         <v>9</v>
@@ -9118,13 +9124,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W16">
         <v>0.0833</v>
@@ -9214,10 +9220,10 @@
         <v>239.3</v>
       </c>
       <c r="AZ16" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BA16" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BB16">
         <v>94.90000000000001</v>
@@ -9304,7 +9310,7 @@
         <v>1.1511</v>
       </c>
       <c r="CD16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE16">
         <v>1844</v>
@@ -9352,13 +9358,13 @@
         <v>26.4</v>
       </c>
       <c r="CT16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU16">
         <v>21.7</v>
       </c>
       <c r="CV16" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CW16">
         <v>87</v>
@@ -9387,22 +9393,22 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H17" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I17" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J17">
-        <v>413.6</v>
+        <v>415.1</v>
       </c>
       <c r="K17">
         <v>10</v>
@@ -9432,13 +9438,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W17">
         <v>0.0833</v>
@@ -9528,10 +9534,10 @@
         <v>228.6</v>
       </c>
       <c r="AZ17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA17" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB17">
         <v>87.8</v>
@@ -9618,7 +9624,7 @@
         <v>1.1569</v>
       </c>
       <c r="CD17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE17">
         <v>1656</v>
@@ -9666,13 +9672,13 @@
         <v>21.7</v>
       </c>
       <c r="CT17" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU17">
         <v>6.4</v>
       </c>
       <c r="CV17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW17">
         <v>84</v>
@@ -9701,22 +9707,22 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F18" t="s">
         <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H18" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J18">
-        <v>110.7</v>
+        <v>112.1</v>
       </c>
       <c r="K18">
         <v>7.6</v>
@@ -9746,13 +9752,13 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U18" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W18">
         <v>0.6667</v>
@@ -9842,10 +9848,10 @@
         <v>225.8</v>
       </c>
       <c r="AZ18" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA18" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB18">
         <v>96.40000000000001</v>
@@ -9932,7 +9938,7 @@
         <v>1.125</v>
       </c>
       <c r="CD18" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE18">
         <v>2605</v>
@@ -9980,13 +9986,13 @@
         <v>24.4</v>
       </c>
       <c r="CT18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU18">
         <v>3.3</v>
       </c>
       <c r="CV18" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW18">
         <v>83</v>
@@ -10015,22 +10021,22 @@
         <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F19" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H19" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J19">
-        <v>110.7</v>
+        <v>112.1</v>
       </c>
       <c r="K19">
         <v>8.6</v>
@@ -10060,13 +10066,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U19" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W19">
         <v>0.6667</v>
@@ -10156,10 +10162,10 @@
         <v>217.4</v>
       </c>
       <c r="AZ19" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA19" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB19">
         <v>94.90000000000001</v>
@@ -10246,7 +10252,7 @@
         <v>1.1306</v>
       </c>
       <c r="CD19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE19">
         <v>2430</v>
@@ -10294,13 +10300,13 @@
         <v>27.5</v>
       </c>
       <c r="CT19" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU19">
         <v>2.5</v>
       </c>
       <c r="CV19" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW19">
         <v>80</v>
@@ -10329,22 +10335,22 @@
         <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F20" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G20" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H20" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J20">
-        <v>110.7</v>
+        <v>112.1</v>
       </c>
       <c r="K20">
         <v>9.6</v>
@@ -10374,13 +10380,13 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U20" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V20" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W20">
         <v>0.6667</v>
@@ -10407,7 +10413,7 @@
         <v>0.2</v>
       </c>
       <c r="AE20" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AF20">
         <v>77.7</v>
@@ -10470,10 +10476,10 @@
         <v>217.3</v>
       </c>
       <c r="AZ20" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA20" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB20">
         <v>95.59999999999999</v>
@@ -10560,7 +10566,7 @@
         <v>1.1369</v>
       </c>
       <c r="CD20" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE20">
         <v>2238</v>
@@ -10608,13 +10614,13 @@
         <v>32.2</v>
       </c>
       <c r="CT20" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU20">
         <v>15.6</v>
       </c>
       <c r="CV20" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW20">
         <v>77</v>
@@ -10643,22 +10649,22 @@
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F21" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G21" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H21" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I21" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J21">
-        <v>110.7</v>
+        <v>112.1</v>
       </c>
       <c r="K21">
         <v>10.6</v>
@@ -10688,13 +10694,13 @@
         <v>25</v>
       </c>
       <c r="T21" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U21" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V21" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W21">
         <v>0.6667</v>
@@ -10721,7 +10727,7 @@
         <v>0.2</v>
       </c>
       <c r="AE21" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AF21">
         <v>75.7</v>
@@ -10778,16 +10784,16 @@
         <v>6.4</v>
       </c>
       <c r="AX21" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AY21">
         <v>212.2</v>
       </c>
       <c r="AZ21" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA21" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB21">
         <v>90</v>
@@ -10874,7 +10880,7 @@
         <v>1.1419</v>
       </c>
       <c r="CD21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE21">
         <v>2086</v>
@@ -10922,13 +10928,13 @@
         <v>35.6</v>
       </c>
       <c r="CT21" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU21">
         <v>16.4</v>
       </c>
       <c r="CV21" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW21">
         <v>75</v>
@@ -10957,22 +10963,22 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F22" t="s">
         <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H22" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I22" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J22">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="K22">
         <v>7.7</v>
@@ -11002,13 +11008,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U22" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V22" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W22">
         <v>0.75</v>
@@ -11098,10 +11104,10 @@
         <v>227.1</v>
       </c>
       <c r="AZ22" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA22" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB22">
         <v>86.40000000000001</v>
@@ -11188,7 +11194,7 @@
         <v>1.1429</v>
       </c>
       <c r="CD22" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE22">
         <v>2135</v>
@@ -11236,13 +11242,13 @@
         <v>22.7</v>
       </c>
       <c r="CT22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU22">
         <v>8.800000000000001</v>
       </c>
       <c r="CV22" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW22">
         <v>88</v>
@@ -11271,22 +11277,22 @@
         <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F23" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G23" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H23" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J23">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="K23">
         <v>8.699999999999999</v>
@@ -11316,13 +11322,13 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U23" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V23" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W23">
         <v>0.75</v>
@@ -11412,10 +11418,10 @@
         <v>253.6</v>
       </c>
       <c r="AZ23" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BA23" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="BB23">
         <v>73.40000000000001</v>
@@ -11502,7 +11508,7 @@
         <v>1.1524</v>
       </c>
       <c r="CD23" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE23">
         <v>1813</v>
@@ -11550,13 +11556,13 @@
         <v>22</v>
       </c>
       <c r="CT23" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU23">
         <v>4.9</v>
       </c>
       <c r="CV23" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW23">
         <v>84</v>
@@ -11585,22 +11591,22 @@
         <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F24" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G24" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H24" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I24" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J24">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="K24">
         <v>9.699999999999999</v>
@@ -11630,13 +11636,13 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V24" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W24">
         <v>0.75</v>
@@ -11726,10 +11732,10 @@
         <v>221.9</v>
       </c>
       <c r="AZ24" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BA24" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="BB24">
         <v>86.3</v>
@@ -11816,7 +11822,7 @@
         <v>1.1574</v>
       </c>
       <c r="CD24" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE24">
         <v>1646</v>
@@ -11864,13 +11870,13 @@
         <v>20.5</v>
       </c>
       <c r="CT24" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU24">
         <v>4.9</v>
       </c>
       <c r="CV24" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW24">
         <v>82</v>
@@ -11899,22 +11905,22 @@
         <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G25" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H25" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J25">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="K25">
         <v>10.7</v>
@@ -11944,13 +11950,13 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U25" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V25" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W25">
         <v>0.75</v>
@@ -12034,16 +12040,16 @@
         <v>4.5</v>
       </c>
       <c r="AX25" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AY25">
         <v>200.9</v>
       </c>
       <c r="AZ25" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="BA25" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="BB25">
         <v>90.5</v>
@@ -12130,7 +12136,7 @@
         <v>1.1618</v>
       </c>
       <c r="CD25" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE25">
         <v>1506</v>
@@ -12178,13 +12184,13 @@
         <v>20.4</v>
       </c>
       <c r="CT25" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="CU25">
         <v>5.4</v>
       </c>
       <c r="CV25" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW25">
         <v>82</v>
@@ -12213,22 +12219,22 @@
         <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F26" t="s">
         <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J26">
-        <v>460.6</v>
+        <v>462</v>
       </c>
       <c r="K26">
         <v>8.1</v>
@@ -12258,13 +12264,13 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U26" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V26" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W26">
         <v>0.1667</v>
@@ -12354,10 +12360,10 @@
         <v>135.4</v>
       </c>
       <c r="AZ26" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA26" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB26">
         <v>95.09999999999999</v>
@@ -12444,7 +12450,7 @@
         <v>1.1094</v>
       </c>
       <c r="CD26" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE26">
         <v>3114</v>
@@ -12492,13 +12498,13 @@
         <v>12.6</v>
       </c>
       <c r="CT26" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU26">
         <v>3.5</v>
       </c>
       <c r="CV26" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW26">
         <v>89</v>
@@ -12527,22 +12533,22 @@
         <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F27" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G27" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H27" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I27" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J27">
-        <v>460.6</v>
+        <v>462</v>
       </c>
       <c r="K27">
         <v>9.1</v>
@@ -12572,13 +12578,13 @@
         <v>18.8</v>
       </c>
       <c r="T27" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U27" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V27" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W27">
         <v>0.1667</v>
@@ -12668,10 +12674,10 @@
         <v>132.4</v>
       </c>
       <c r="AZ27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB27">
         <v>92.5</v>
@@ -12758,7 +12764,7 @@
         <v>1.1106</v>
       </c>
       <c r="CD27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE27">
         <v>3058</v>
@@ -12806,13 +12812,13 @@
         <v>13.4</v>
       </c>
       <c r="CT27" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU27">
         <v>3.8</v>
       </c>
       <c r="CV27" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW27">
         <v>89</v>
@@ -12841,22 +12847,22 @@
         <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F28" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G28" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I28" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J28">
-        <v>460.6</v>
+        <v>462</v>
       </c>
       <c r="K28">
         <v>10.1</v>
@@ -12886,13 +12892,13 @@
         <v>56.2</v>
       </c>
       <c r="T28" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U28" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V28" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W28">
         <v>0.1667</v>
@@ -12982,10 +12988,10 @@
         <v>131.7</v>
       </c>
       <c r="AZ28" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA28" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB28">
         <v>90.40000000000001</v>
@@ -13072,7 +13078,7 @@
         <v>1.1153</v>
       </c>
       <c r="CD28" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE28">
         <v>2909</v>
@@ -13120,13 +13126,13 @@
         <v>12.5</v>
       </c>
       <c r="CT28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU28">
         <v>5.1</v>
       </c>
       <c r="CV28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW28">
         <v>87</v>
@@ -13155,22 +13161,22 @@
         <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F29" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G29" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H29" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J29">
-        <v>460.6</v>
+        <v>462</v>
       </c>
       <c r="K29">
         <v>11.1</v>
@@ -13200,13 +13206,13 @@
         <v>56.2</v>
       </c>
       <c r="T29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U29" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V29" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W29">
         <v>0.1667</v>
@@ -13296,10 +13302,10 @@
         <v>131.3</v>
       </c>
       <c r="AZ29" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA29" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB29">
         <v>90.59999999999999</v>
@@ -13386,7 +13392,7 @@
         <v>1.1212</v>
       </c>
       <c r="CD29" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE29">
         <v>2736</v>
@@ -13434,13 +13440,13 @@
         <v>12.7</v>
       </c>
       <c r="CT29" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU29">
         <v>2.4</v>
       </c>
       <c r="CV29" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW29">
         <v>84</v>
@@ -13469,22 +13475,22 @@
         <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F30" t="s">
         <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H30" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I30" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J30">
-        <v>30.5</v>
+        <v>31.9</v>
       </c>
       <c r="K30">
         <v>8.1</v>
@@ -13514,13 +13520,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U30" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V30" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W30">
         <v>0.1667</v>
@@ -13610,10 +13616,10 @@
         <v>277.9</v>
       </c>
       <c r="AZ30" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA30" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB30">
         <v>96.7</v>
@@ -13700,7 +13706,7 @@
         <v>1.1418</v>
       </c>
       <c r="CD30" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE30">
         <v>2240</v>
@@ -13748,13 +13754,13 @@
         <v>0</v>
       </c>
       <c r="CT30" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU30">
         <v>5.7</v>
       </c>
       <c r="CV30" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW30">
         <v>81</v>
@@ -13783,22 +13789,22 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F31" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G31" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J31">
-        <v>30.5</v>
+        <v>31.9</v>
       </c>
       <c r="K31">
         <v>9.1</v>
@@ -13828,13 +13834,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U31" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V31" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W31">
         <v>0.1667</v>
@@ -13924,10 +13930,10 @@
         <v>270.2</v>
       </c>
       <c r="AZ31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB31">
         <v>98</v>
@@ -14014,7 +14020,7 @@
         <v>1.1445</v>
       </c>
       <c r="CD31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE31">
         <v>2152</v>
@@ -14062,13 +14068,13 @@
         <v>0</v>
       </c>
       <c r="CT31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU31">
         <v>3.1</v>
       </c>
       <c r="CV31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW31">
         <v>80</v>
@@ -14097,22 +14103,22 @@
         <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F32" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G32" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H32" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I32" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J32">
-        <v>30.5</v>
+        <v>31.9</v>
       </c>
       <c r="K32">
         <v>10.1</v>
@@ -14142,13 +14148,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U32" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V32" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W32">
         <v>0.1667</v>
@@ -14238,10 +14244,10 @@
         <v>250.9</v>
       </c>
       <c r="AZ32" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BA32" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BB32">
         <v>89.59999999999999</v>
@@ -14328,7 +14334,7 @@
         <v>1.1505</v>
       </c>
       <c r="CD32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE32">
         <v>1961</v>
@@ -14376,13 +14382,13 @@
         <v>0.2</v>
       </c>
       <c r="CT32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU32">
         <v>2.7</v>
       </c>
       <c r="CV32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW32">
         <v>77</v>
@@ -14411,22 +14417,22 @@
         <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F33" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G33" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H33" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I33" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J33">
-        <v>30.5</v>
+        <v>31.9</v>
       </c>
       <c r="K33">
         <v>11.1</v>
@@ -14456,13 +14462,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U33" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V33" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W33">
         <v>0.1667</v>
@@ -14552,10 +14558,10 @@
         <v>237.5</v>
       </c>
       <c r="AZ33" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA33" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB33">
         <v>67.2</v>
@@ -14642,7 +14648,7 @@
         <v>1.1571</v>
       </c>
       <c r="CD33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE33">
         <v>1749</v>
@@ -14690,13 +14696,13 @@
         <v>0.3</v>
       </c>
       <c r="CT33" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU33">
         <v>7.4</v>
       </c>
       <c r="CV33" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW33">
         <v>74</v>
@@ -14725,22 +14731,22 @@
         <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F34" t="s">
         <v>114</v>
       </c>
       <c r="G34" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H34" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I34" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J34">
-        <v>485.3</v>
+        <v>486.7</v>
       </c>
       <c r="K34">
         <v>8.199999999999999</v>
@@ -14770,13 +14776,13 @@
         <v>100</v>
       </c>
       <c r="T34" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="V34" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="W34">
         <v>0.25</v>
@@ -14866,10 +14872,10 @@
         <v>288.9</v>
       </c>
       <c r="AZ34" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BA34" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BB34">
         <v>90.90000000000001</v>
@@ -14956,7 +14962,7 @@
         <v>1.1649</v>
       </c>
       <c r="CD34" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE34">
         <v>1456</v>
@@ -15004,13 +15010,13 @@
         <v>0</v>
       </c>
       <c r="CT34" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU34">
         <v>8.699999999999999</v>
       </c>
       <c r="CV34" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW34">
         <v>81</v>
@@ -15039,22 +15045,22 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F35" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G35" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I35" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J35">
-        <v>485.3</v>
+        <v>486.7</v>
       </c>
       <c r="K35">
         <v>9.199999999999999</v>
@@ -15084,13 +15090,13 @@
         <v>81.2</v>
       </c>
       <c r="T35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U35" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V35" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="W35">
         <v>0.25</v>
@@ -15180,10 +15186,10 @@
         <v>288.5</v>
       </c>
       <c r="AZ35" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BA35" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BB35">
         <v>89.90000000000001</v>
@@ -15270,7 +15276,7 @@
         <v>1.1674</v>
       </c>
       <c r="CD35" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE35">
         <v>1382</v>
@@ -15318,13 +15324,13 @@
         <v>0.2</v>
       </c>
       <c r="CT35" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU35">
         <v>11.6</v>
       </c>
       <c r="CV35" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW35">
         <v>80</v>
@@ -15353,22 +15359,22 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F36" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G36" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H36" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I36" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J36">
-        <v>485.3</v>
+        <v>486.7</v>
       </c>
       <c r="K36">
         <v>10.2</v>
@@ -15398,13 +15404,13 @@
         <v>56.2</v>
       </c>
       <c r="T36" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U36" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V36" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W36">
         <v>0.25</v>
@@ -15494,10 +15500,10 @@
         <v>288.2</v>
       </c>
       <c r="AZ36" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BA36" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BB36">
         <v>89.3</v>
@@ -15584,7 +15590,7 @@
         <v>1.1706</v>
       </c>
       <c r="CD36" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE36">
         <v>1292</v>
@@ -15632,13 +15638,13 @@
         <v>0.2</v>
       </c>
       <c r="CT36" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU36">
         <v>14.2</v>
       </c>
       <c r="CV36" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW36">
         <v>79</v>
@@ -15667,22 +15673,22 @@
         <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F37" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G37" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H37" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I37" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J37">
-        <v>485.3</v>
+        <v>486.7</v>
       </c>
       <c r="K37">
         <v>11.2</v>
@@ -15712,13 +15718,13 @@
         <v>81.2</v>
       </c>
       <c r="T37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U37" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V37" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W37">
         <v>0.25</v>
@@ -15802,16 +15808,16 @@
         <v>4.3</v>
       </c>
       <c r="AX37" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AY37">
         <v>309.5</v>
       </c>
       <c r="AZ37" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BA37" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="BB37">
         <v>90.5</v>
@@ -15898,7 +15904,7 @@
         <v>1.1757</v>
       </c>
       <c r="CD37" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE37">
         <v>1140</v>
@@ -15946,13 +15952,13 @@
         <v>0.2</v>
       </c>
       <c r="CT37" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU37">
         <v>8.199999999999999</v>
       </c>
       <c r="CV37" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW37">
         <v>76</v>
@@ -15981,22 +15987,22 @@
         <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F38" t="s">
         <v>114</v>
       </c>
       <c r="G38" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H38" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I38" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J38">
-        <v>370.2</v>
+        <v>371.6</v>
       </c>
       <c r="K38">
         <v>8.199999999999999</v>
@@ -16026,13 +16032,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U38" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="V38" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="W38">
         <v>0.25</v>
@@ -16122,10 +16128,10 @@
         <v>241.5</v>
       </c>
       <c r="AZ38" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA38" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB38">
         <v>88.3</v>
@@ -16212,7 +16218,7 @@
         <v>1.2164</v>
       </c>
       <c r="CD38" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE38">
         <v>50</v>
@@ -16260,13 +16266,13 @@
         <v>0.4</v>
       </c>
       <c r="CT38" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU38">
         <v>14.4</v>
       </c>
       <c r="CV38" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW38">
         <v>65</v>
@@ -16295,22 +16301,22 @@
         <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F39" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G39" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H39" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I39" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J39">
-        <v>370.2</v>
+        <v>371.6</v>
       </c>
       <c r="K39">
         <v>9.199999999999999</v>
@@ -16340,13 +16346,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U39" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V39" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="W39">
         <v>0.25</v>
@@ -16436,10 +16442,10 @@
         <v>237.3</v>
       </c>
       <c r="AZ39" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA39" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB39">
         <v>83.2</v>
@@ -16526,7 +16532,7 @@
         <v>1.2153</v>
       </c>
       <c r="CD39" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE39">
         <v>76</v>
@@ -16574,13 +16580,13 @@
         <v>0.5</v>
       </c>
       <c r="CT39" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU39">
         <v>16.6</v>
       </c>
       <c r="CV39" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW39">
         <v>66</v>
@@ -16609,22 +16615,22 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F40" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G40" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H40" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I40" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J40">
-        <v>370.2</v>
+        <v>371.6</v>
       </c>
       <c r="K40">
         <v>10.2</v>
@@ -16654,13 +16660,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V40" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W40">
         <v>0.25</v>
@@ -16750,10 +16756,10 @@
         <v>231.4</v>
       </c>
       <c r="AZ40" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BA40" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="BB40">
         <v>80.2</v>
@@ -16840,7 +16846,7 @@
         <v>1.2167</v>
       </c>
       <c r="CD40" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE40">
         <v>36</v>
@@ -16888,13 +16894,13 @@
         <v>0.5</v>
       </c>
       <c r="CT40" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU40">
         <v>16.9</v>
       </c>
       <c r="CV40" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW40">
         <v>65</v>
@@ -16923,22 +16929,22 @@
         <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F41" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G41" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H41" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J41">
-        <v>370.2</v>
+        <v>371.6</v>
       </c>
       <c r="K41">
         <v>11.2</v>
@@ -16968,13 +16974,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U41" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V41" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W41">
         <v>0.25</v>
@@ -17064,10 +17070,10 @@
         <v>214.4</v>
       </c>
       <c r="AZ41" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BA41" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BB41">
         <v>78.3</v>
@@ -17154,7 +17160,7 @@
         <v>1.2181</v>
       </c>
       <c r="CD41" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE41">
         <v>-4</v>
@@ -17202,13 +17208,13 @@
         <v>0.5</v>
       </c>
       <c r="CT41" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU41">
         <v>14.9</v>
       </c>
       <c r="CV41" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW41">
         <v>64</v>
@@ -17237,22 +17243,22 @@
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F42" t="s">
         <v>115</v>
       </c>
       <c r="G42" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H42" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I42" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J42">
-        <v>205.9</v>
+        <v>207.3</v>
       </c>
       <c r="K42">
         <v>8.199999999999999</v>
@@ -17282,13 +17288,13 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U42" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V42" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W42">
         <v>0.25</v>
@@ -17378,10 +17384,10 @@
         <v>164.9</v>
       </c>
       <c r="AZ42" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA42" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB42">
         <v>89.40000000000001</v>
@@ -17468,7 +17474,7 @@
         <v>1.1299</v>
       </c>
       <c r="CD42" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE42">
         <v>2471</v>
@@ -17516,13 +17522,13 @@
         <v>12.8</v>
       </c>
       <c r="CT42" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU42">
         <v>5.7</v>
       </c>
       <c r="CV42" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW42">
         <v>89</v>
@@ -17551,22 +17557,22 @@
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F43" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G43" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H43" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I43" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J43">
-        <v>205.9</v>
+        <v>207.3</v>
       </c>
       <c r="K43">
         <v>9.199999999999999</v>
@@ -17596,13 +17602,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U43" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V43" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W43">
         <v>0.25</v>
@@ -17692,10 +17698,10 @@
         <v>157.6</v>
       </c>
       <c r="AZ43" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA43" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB43">
         <v>87.7</v>
@@ -17782,7 +17788,7 @@
         <v>1.1327</v>
       </c>
       <c r="CD43" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE43">
         <v>2378</v>
@@ -17830,13 +17836,13 @@
         <v>12.7</v>
       </c>
       <c r="CT43" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU43">
         <v>5.6</v>
       </c>
       <c r="CV43" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW43">
         <v>88</v>
@@ -17865,22 +17871,22 @@
         <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F44" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G44" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H44" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I44" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J44">
-        <v>205.9</v>
+        <v>207.3</v>
       </c>
       <c r="K44">
         <v>10.2</v>
@@ -17910,13 +17916,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U44" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V44" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W44">
         <v>0.25</v>
@@ -18006,10 +18012,10 @@
         <v>147.2</v>
       </c>
       <c r="AZ44" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA44" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB44">
         <v>90</v>
@@ -18096,7 +18102,7 @@
         <v>1.1386</v>
       </c>
       <c r="CD44" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE44">
         <v>2184</v>
@@ -18144,13 +18150,13 @@
         <v>12.6</v>
       </c>
       <c r="CT44" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU44">
         <v>5.2</v>
       </c>
       <c r="CV44" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW44">
         <v>85</v>
@@ -18179,22 +18185,22 @@
         <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F45" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G45" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H45" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I45" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J45">
-        <v>205.9</v>
+        <v>207.3</v>
       </c>
       <c r="K45">
         <v>11.2</v>
@@ -18224,13 +18230,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U45" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V45" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W45">
         <v>0.25</v>
@@ -18320,10 +18326,10 @@
         <v>146.3</v>
       </c>
       <c r="AZ45" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BA45" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="BB45">
         <v>81.2</v>
@@ -18410,7 +18416,7 @@
         <v>1.1458</v>
       </c>
       <c r="CD45" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE45">
         <v>1964</v>
@@ -18458,13 +18464,13 @@
         <v>12.2</v>
       </c>
       <c r="CT45" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU45">
         <v>5.2</v>
       </c>
       <c r="CV45" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW45">
         <v>81</v>
@@ -18493,22 +18499,22 @@
         <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F46" t="s">
         <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H46" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I46" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J46">
-        <v>125.3</v>
+        <v>126.7</v>
       </c>
       <c r="K46">
         <v>8.199999999999999</v>
@@ -18538,13 +18544,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U46" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V46" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W46">
         <v>0.25</v>
@@ -18634,10 +18640,10 @@
         <v>149.9</v>
       </c>
       <c r="AZ46" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BA46" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BB46">
         <v>95.09999999999999</v>
@@ -18724,7 +18730,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD46" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE46">
         <v>858</v>
@@ -18772,13 +18778,13 @@
         <v>0</v>
       </c>
       <c r="CT46" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU46">
         <v>5.1</v>
       </c>
       <c r="CV46" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW46">
         <v>99</v>
@@ -18807,22 +18813,22 @@
         <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F47" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G47" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H47" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I47" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J47">
-        <v>125.3</v>
+        <v>126.7</v>
       </c>
       <c r="K47">
         <v>9.199999999999999</v>
@@ -18852,13 +18858,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U47" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V47" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W47">
         <v>0.25</v>
@@ -18948,10 +18954,10 @@
         <v>155.4</v>
       </c>
       <c r="AZ47" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BA47" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BB47">
         <v>95.2</v>
@@ -19038,7 +19044,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD47" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE47">
         <v>858</v>
@@ -19086,13 +19092,13 @@
         <v>0</v>
       </c>
       <c r="CT47" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU47">
         <v>5.5</v>
       </c>
       <c r="CV47" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW47">
         <v>98</v>
@@ -19121,22 +19127,22 @@
         <v>129</v>
       </c>
       <c r="E48" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F48" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G48" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H48" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I48" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J48">
-        <v>125.3</v>
+        <v>126.7</v>
       </c>
       <c r="K48">
         <v>10.2</v>
@@ -19166,13 +19172,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U48" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V48" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W48">
         <v>0.25</v>
@@ -19262,10 +19268,10 @@
         <v>145.1</v>
       </c>
       <c r="AZ48" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BA48" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BB48">
         <v>93.40000000000001</v>
@@ -19352,7 +19358,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD48" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE48">
         <v>858</v>
@@ -19400,13 +19406,13 @@
         <v>0</v>
       </c>
       <c r="CT48" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU48">
         <v>6.6</v>
       </c>
       <c r="CV48" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW48">
         <v>95</v>
@@ -19435,22 +19441,22 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F49" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G49" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H49" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I49" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J49">
-        <v>125.3</v>
+        <v>126.7</v>
       </c>
       <c r="K49">
         <v>11.2</v>
@@ -19480,13 +19486,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U49" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V49" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W49">
         <v>0.25</v>
@@ -19576,10 +19582,10 @@
         <v>168</v>
       </c>
       <c r="AZ49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BA49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="BB49">
         <v>89.7</v>
@@ -19666,7 +19672,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD49" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE49">
         <v>858</v>
@@ -19714,13 +19720,13 @@
         <v>0</v>
       </c>
       <c r="CT49" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU49">
         <v>10.5</v>
       </c>
       <c r="CV49" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW49">
         <v>92</v>
@@ -19749,22 +19755,22 @@
         <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F50" t="s">
         <v>115</v>
       </c>
       <c r="G50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H50" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I50" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J50">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="K50">
         <v>8.199999999999999</v>
@@ -19794,13 +19800,13 @@
         <v>75</v>
       </c>
       <c r="T50" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U50" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V50" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W50">
         <v>0.25</v>
@@ -19890,10 +19896,10 @@
         <v>105.1</v>
       </c>
       <c r="AZ50" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA50" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB50">
         <v>56.4</v>
@@ -19980,7 +19986,7 @@
         <v>1.1488</v>
       </c>
       <c r="CD50" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE50">
         <v>1955</v>
@@ -20028,13 +20034,13 @@
         <v>3.4</v>
       </c>
       <c r="CT50" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU50">
         <v>4.9</v>
       </c>
       <c r="CV50" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW50">
         <v>78</v>
@@ -20063,22 +20069,22 @@
         <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F51" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G51" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H51" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I51" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J51">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="K51">
         <v>9.199999999999999</v>
@@ -20108,13 +20114,13 @@
         <v>75</v>
       </c>
       <c r="T51" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U51" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V51" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W51">
         <v>0.25</v>
@@ -20204,10 +20210,10 @@
         <v>112</v>
       </c>
       <c r="AZ51" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA51" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB51">
         <v>46.6</v>
@@ -20294,7 +20300,7 @@
         <v>1.1522</v>
       </c>
       <c r="CD51" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE51">
         <v>1844</v>
@@ -20342,13 +20348,13 @@
         <v>4.4</v>
       </c>
       <c r="CT51" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU51">
         <v>6.2</v>
       </c>
       <c r="CV51" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW51">
         <v>77</v>
@@ -20377,22 +20383,22 @@
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F52" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G52" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H52" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I52" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J52">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="K52">
         <v>10.2</v>
@@ -20422,13 +20428,13 @@
         <v>75</v>
       </c>
       <c r="T52" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U52" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V52" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W52">
         <v>0.25</v>
@@ -20518,10 +20524,10 @@
         <v>126.6</v>
       </c>
       <c r="AZ52" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BA52" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BB52">
         <v>48.9</v>
@@ -20608,7 +20614,7 @@
         <v>1.1568</v>
       </c>
       <c r="CD52" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="CE52">
         <v>1698</v>
@@ -20656,13 +20662,13 @@
         <v>4.4</v>
       </c>
       <c r="CT52" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU52">
         <v>7.2</v>
       </c>
       <c r="CV52" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW52">
         <v>75</v>
@@ -20691,22 +20697,22 @@
         <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F53" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G53" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H53" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I53" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J53">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="K53">
         <v>11.2</v>
@@ -20736,13 +20742,13 @@
         <v>75</v>
       </c>
       <c r="T53" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U53" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V53" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W53">
         <v>0.25</v>
@@ -20832,10 +20838,10 @@
         <v>129.7</v>
       </c>
       <c r="AZ53" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BA53" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BB53">
         <v>59.8</v>
@@ -20922,7 +20928,7 @@
         <v>1.1603</v>
       </c>
       <c r="CD53" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE53">
         <v>1591</v>
@@ -20970,13 +20976,13 @@
         <v>3.4</v>
       </c>
       <c r="CT53" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU53">
         <v>7.9</v>
       </c>
       <c r="CV53" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW53">
         <v>74</v>
@@ -21005,22 +21011,22 @@
         <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F54" t="s">
         <v>116</v>
       </c>
       <c r="G54" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H54" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I54" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J54">
-        <v>429.9</v>
+        <v>431.2</v>
       </c>
       <c r="K54">
         <v>9.1</v>
@@ -21050,13 +21056,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U54" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V54" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="W54">
         <v>0.1667</v>
@@ -21146,10 +21152,10 @@
         <v>227.2</v>
       </c>
       <c r="AZ54" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="BA54" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="BB54">
         <v>23.4</v>
@@ -21236,7 +21242,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD54" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE54">
         <v>858</v>
@@ -21284,13 +21290,13 @@
         <v>0</v>
       </c>
       <c r="CT54" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU54">
         <v>8.699999999999999</v>
       </c>
       <c r="CV54" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW54">
         <v>112</v>
@@ -21319,22 +21325,22 @@
         <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F55" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G55" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H55" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I55" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J55">
-        <v>429.9</v>
+        <v>431.2</v>
       </c>
       <c r="K55">
         <v>10.1</v>
@@ -21364,13 +21370,13 @@
         <v>56.2</v>
       </c>
       <c r="T55" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U55" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V55" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W55">
         <v>0.1667</v>
@@ -21397,7 +21403,7 @@
         <v>0.4</v>
       </c>
       <c r="AE55" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AF55">
         <v>109.1</v>
@@ -21454,16 +21460,16 @@
         <v>0</v>
       </c>
       <c r="AX55" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AY55">
         <v>56.4</v>
       </c>
       <c r="AZ55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BA55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BB55">
         <v>43.3</v>
@@ -21550,7 +21556,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD55" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE55">
         <v>858</v>
@@ -21598,13 +21604,13 @@
         <v>0</v>
       </c>
       <c r="CT55" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU55">
         <v>4.1</v>
       </c>
       <c r="CV55" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW55">
         <v>110</v>
@@ -21633,22 +21639,22 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F56" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G56" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H56" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I56" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J56">
-        <v>429.9</v>
+        <v>431.2</v>
       </c>
       <c r="K56">
         <v>11.1</v>
@@ -21678,13 +21684,13 @@
         <v>75</v>
       </c>
       <c r="T56" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U56" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V56" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W56">
         <v>0.1667</v>
@@ -21711,7 +21717,7 @@
         <v>0.4</v>
       </c>
       <c r="AE56" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AF56">
         <v>102.2</v>
@@ -21768,16 +21774,16 @@
         <v>0</v>
       </c>
       <c r="AX56" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AY56">
         <v>322.3</v>
       </c>
       <c r="AZ56" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BA56" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BB56">
         <v>41.3</v>
@@ -21864,7 +21870,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD56" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE56">
         <v>858</v>
@@ -21912,13 +21918,13 @@
         <v>0</v>
       </c>
       <c r="CT56" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU56">
         <v>26</v>
       </c>
       <c r="CV56" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CW56">
         <v>109</v>
@@ -21947,22 +21953,22 @@
         <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F57" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G57" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H57" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I57" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J57">
-        <v>429.9</v>
+        <v>431.2</v>
       </c>
       <c r="K57">
         <v>12.1</v>
@@ -21992,13 +21998,13 @@
         <v>75</v>
       </c>
       <c r="T57" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U57" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V57" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W57">
         <v>0.1667</v>
@@ -22025,7 +22031,7 @@
         <v>0.4</v>
       </c>
       <c r="AE57" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AF57">
         <v>101.4</v>
@@ -22082,16 +22088,16 @@
         <v>0</v>
       </c>
       <c r="AX57" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AY57">
         <v>330.6</v>
       </c>
       <c r="AZ57" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BA57" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BB57">
         <v>35.6</v>
@@ -22178,7 +22184,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD57" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE57">
         <v>858</v>
@@ -22226,13 +22232,13 @@
         <v>0</v>
       </c>
       <c r="CT57" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CU57">
         <v>18.1</v>
       </c>
       <c r="CV57" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="CW57">
         <v>105</v>
@@ -22261,22 +22267,22 @@
         <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F58" t="s">
         <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H58" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I58" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J58">
-        <v>436.5</v>
+        <v>437.9</v>
       </c>
       <c r="K58">
         <v>10.8</v>
@@ -22306,13 +22312,13 @@
         <v>100</v>
       </c>
       <c r="T58" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U58" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V58" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W58">
         <v>0.8333</v>
@@ -22402,10 +22408,10 @@
         <v>19.7</v>
       </c>
       <c r="AZ58" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA58" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB58">
         <v>90.59999999999999</v>
@@ -22492,7 +22498,7 @@
         <v>1.1768</v>
       </c>
       <c r="CD58" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE58">
         <v>1223</v>
@@ -22540,13 +22546,13 @@
         <v>0</v>
       </c>
       <c r="CT58" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU58">
         <v>2.7</v>
       </c>
       <c r="CV58" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW58">
         <v>78</v>
@@ -22575,22 +22581,22 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F59" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G59" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H59" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I59" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J59">
-        <v>436.5</v>
+        <v>437.9</v>
       </c>
       <c r="K59">
         <v>11.8</v>
@@ -22620,13 +22626,13 @@
         <v>100</v>
       </c>
       <c r="T59" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U59" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V59" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W59">
         <v>0.8333</v>
@@ -22710,16 +22716,16 @@
         <v>5.5</v>
       </c>
       <c r="AX59" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AY59">
         <v>35.4</v>
       </c>
       <c r="AZ59" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BA59" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="BB59">
         <v>88.3</v>
@@ -22806,7 +22812,7 @@
         <v>1.1856</v>
       </c>
       <c r="CD59" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE59">
         <v>959</v>
@@ -22854,13 +22860,13 @@
         <v>0</v>
       </c>
       <c r="CT59" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU59">
         <v>3.6</v>
       </c>
       <c r="CV59" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW59">
         <v>74</v>
@@ -22889,22 +22895,22 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F60" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G60" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H60" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I60" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J60">
-        <v>436.5</v>
+        <v>437.9</v>
       </c>
       <c r="K60">
         <v>12.8</v>
@@ -22934,13 +22940,13 @@
         <v>81.2</v>
       </c>
       <c r="T60" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U60" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="V60" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="W60">
         <v>0.8333</v>
@@ -23024,16 +23030,16 @@
         <v>6.1</v>
       </c>
       <c r="AX60" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AY60">
         <v>44</v>
       </c>
       <c r="AZ60" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BA60" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BB60">
         <v>80.59999999999999</v>
@@ -23120,7 +23126,7 @@
         <v>1.1941</v>
       </c>
       <c r="CD60" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE60">
         <v>712</v>
@@ -23168,13 +23174,13 @@
         <v>0</v>
       </c>
       <c r="CT60" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU60">
         <v>6.5</v>
       </c>
       <c r="CV60" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW60">
         <v>71</v>
@@ -23203,22 +23209,22 @@
         <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F61" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G61" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I61" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J61">
-        <v>436.5</v>
+        <v>437.9</v>
       </c>
       <c r="K61">
         <v>13.8</v>
@@ -23248,13 +23254,13 @@
         <v>81.2</v>
       </c>
       <c r="T61" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U61" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="V61" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W61">
         <v>0.8333</v>
@@ -23338,16 +23344,16 @@
         <v>6.1</v>
       </c>
       <c r="AX61" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AY61">
         <v>51.8</v>
       </c>
       <c r="AZ61" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BA61" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="BB61">
         <v>73.09999999999999</v>
@@ -23434,7 +23440,7 @@
         <v>1.2011</v>
       </c>
       <c r="CD61" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="CE61">
         <v>508</v>
@@ -23482,13 +23488,13 @@
         <v>0</v>
       </c>
       <c r="CT61" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CU61">
         <v>9.4</v>
       </c>
       <c r="CV61" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="CW61">
         <v>68</v>
@@ -23635,7 +23641,7 @@
         <v>133</v>
       </c>
       <c r="P2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -23688,7 +23694,7 @@
         <v>133</v>
       </c>
       <c r="P3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -23741,7 +23747,7 @@
         <v>133</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -23794,7 +23800,7 @@
         <v>133</v>
       </c>
       <c r="P5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -23847,7 +23853,7 @@
         <v>133</v>
       </c>
       <c r="P6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -23900,7 +23906,7 @@
         <v>133</v>
       </c>
       <c r="P7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -23953,7 +23959,7 @@
         <v>133</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -24006,7 +24012,7 @@
         <v>133</v>
       </c>
       <c r="P9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -24059,7 +24065,7 @@
         <v>133</v>
       </c>
       <c r="P10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -24112,7 +24118,7 @@
         <v>133</v>
       </c>
       <c r="P11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -24165,7 +24171,7 @@
         <v>133</v>
       </c>
       <c r="P12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -24218,7 +24224,7 @@
         <v>134</v>
       </c>
       <c r="P13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -24271,7 +24277,7 @@
         <v>134</v>
       </c>
       <c r="P14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -24324,7 +24330,7 @@
         <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -24377,7 +24383,7 @@
         <v>133</v>
       </c>
       <c r="P16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q16">
         <v>5</v>

--- a/mlb_weather_professional_v5_2026_08_08.xlsx
+++ b/mlb_weather_professional_v5_2026_08_08.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="395">
   <si>
     <t>Date</t>
   </si>
@@ -602,49 +602,43 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-08-08 08:42:09 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:10 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:11 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:12 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:13 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:14 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:15 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:16 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:17 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:18 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:19 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:20 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:21 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:22 AM PDT</t>
-  </si>
-  <si>
-    <t>2026-08-08 08:42:23 AM PDT</t>
+    <t>2026-08-08 08:43:50 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:51 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:52 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:53 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:54 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:55 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:56 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:57 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:58 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:43:59 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:44:00 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:44:01 AM PDT</t>
+  </si>
+  <si>
+    <t>2026-08-08 08:44:02 AM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1031,49 +1025,43 @@
     <t>09:50 PM PDT</t>
   </si>
   <si>
-    <t>2026-08-08 15:42:09 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:10 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:11 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:12 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:13 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:14 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:15 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:16 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:17 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:18 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:19 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:20 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:21 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:22 UTC</t>
-  </si>
-  <si>
-    <t>2026-08-08 15:42:23 UTC</t>
+    <t>2026-08-08 15:43:50 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:51 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:52 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:53 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:54 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:55 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:56 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:57 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:58 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:43:59 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:44:00 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:44:01 UTC</t>
+  </si>
+  <si>
+    <t>2026-08-08 15:44:02 UTC</t>
   </si>
   <si>
     <t>2026-08-08T06:28:19+00:00</t>
@@ -2026,7 +2014,7 @@
         <v>193</v>
       </c>
       <c r="AZ2">
-        <v>553.8</v>
+        <v>555.5</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2160,7 +2148,7 @@
         <v>184</v>
       </c>
       <c r="AR3">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AS3">
         <v>-0.17</v>
@@ -2181,10 +2169,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AY3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AZ3">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2252,7 +2240,7 @@
         <v>162</v>
       </c>
       <c r="V4">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W4">
         <v>50</v>
@@ -2330,7 +2318,7 @@
         <v>190</v>
       </c>
       <c r="AV4">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="AW4" t="s">
         <v>190</v>
@@ -2339,10 +2327,10 @@
         <v>7.1</v>
       </c>
       <c r="AY4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AZ4">
-        <v>445.2</v>
+        <v>446.8</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2410,7 +2398,7 @@
         <v>162</v>
       </c>
       <c r="V5">
-        <v>30.9</v>
+        <v>29.5</v>
       </c>
       <c r="W5">
         <v>62.7</v>
@@ -2431,7 +2419,7 @@
         <v>3.8</v>
       </c>
       <c r="AC5">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="AD5" t="s">
         <v>181</v>
@@ -2476,7 +2464,7 @@
         <v>184</v>
       </c>
       <c r="AR5">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="AS5">
         <v>-0.08</v>
@@ -2488,7 +2476,7 @@
         <v>189</v>
       </c>
       <c r="AV5">
-        <v>29.4</v>
+        <v>28.9</v>
       </c>
       <c r="AW5" t="s">
         <v>192</v>
@@ -2497,10 +2485,10 @@
         <v>20.1</v>
       </c>
       <c r="AY5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AZ5">
-        <v>453.6</v>
+        <v>455.3</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2568,7 +2556,7 @@
         <v>162</v>
       </c>
       <c r="V6">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="W6">
         <v>59.4</v>
@@ -2634,7 +2622,7 @@
         <v>186</v>
       </c>
       <c r="AR6">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="AS6">
         <v>-0.5</v>
@@ -2646,7 +2634,7 @@
         <v>189</v>
       </c>
       <c r="AV6">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="AW6" t="s">
         <v>190</v>
@@ -2655,10 +2643,10 @@
         <v>15.1</v>
       </c>
       <c r="AY6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AZ6">
-        <v>150.7</v>
+        <v>152.3</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2726,7 +2714,7 @@
         <v>162</v>
       </c>
       <c r="V7">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="W7">
         <v>61.1</v>
@@ -2792,7 +2780,7 @@
         <v>184</v>
       </c>
       <c r="AR7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS7">
         <v>0.5</v>
@@ -2804,7 +2792,7 @@
         <v>189</v>
       </c>
       <c r="AV7">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="AW7" t="s">
         <v>190</v>
@@ -2813,10 +2801,10 @@
         <v>16.9</v>
       </c>
       <c r="AY7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AZ7">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -2884,7 +2872,7 @@
         <v>162</v>
       </c>
       <c r="V8">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W8">
         <v>61.8</v>
@@ -2905,7 +2893,7 @@
         <v>3.5</v>
       </c>
       <c r="AC8">
-        <v>94.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AD8" t="s">
         <v>181</v>
@@ -2962,7 +2950,7 @@
         <v>190</v>
       </c>
       <c r="AV8">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="AW8" t="s">
         <v>190</v>
@@ -2971,10 +2959,10 @@
         <v>5</v>
       </c>
       <c r="AY8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AZ8">
-        <v>500.6</v>
+        <v>502.3</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3129,10 +3117,10 @@
         <v>6.6</v>
       </c>
       <c r="AY9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AZ9">
-        <v>70.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3266,7 +3254,7 @@
         <v>187</v>
       </c>
       <c r="AR10">
-        <v>-3.9</v>
+        <v>-3.5</v>
       </c>
       <c r="AS10">
         <v>-0.31</v>
@@ -3287,10 +3275,10 @@
         <v>13.9</v>
       </c>
       <c r="AY10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AZ10">
-        <v>525.3</v>
+        <v>527</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3445,10 +3433,10 @@
         <v>17.7</v>
       </c>
       <c r="AY11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AZ11">
-        <v>410.1</v>
+        <v>411.8</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3516,7 +3504,7 @@
         <v>162</v>
       </c>
       <c r="V12">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>59</v>
@@ -3582,7 +3570,7 @@
         <v>187</v>
       </c>
       <c r="AR12">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="AS12">
         <v>-0.98</v>
@@ -3594,7 +3582,7 @@
         <v>190</v>
       </c>
       <c r="AV12">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="AW12" t="s">
         <v>190</v>
@@ -3603,10 +3591,10 @@
         <v>5.7</v>
       </c>
       <c r="AY12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AZ12">
-        <v>245.8</v>
+        <v>247.5</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3674,7 +3662,7 @@
         <v>162</v>
       </c>
       <c r="V13">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="W13">
         <v>50</v>
@@ -3695,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AD13" t="s">
         <v>183</v>
@@ -3761,10 +3749,10 @@
         <v>11.2</v>
       </c>
       <c r="AY13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ13">
-        <v>165.2</v>
+        <v>166.9</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3919,10 +3907,10 @@
         <v>7.2</v>
       </c>
       <c r="AY14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ14">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4011,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="AD15" t="s">
         <v>183</v>
@@ -4077,10 +4065,10 @@
         <v>21.8</v>
       </c>
       <c r="AY15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AZ15">
-        <v>469.8</v>
+        <v>471.5</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4214,7 +4202,7 @@
         <v>188</v>
       </c>
       <c r="AR16">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="AS16">
         <v>0.48</v>
@@ -4235,10 +4223,10 @@
         <v>9</v>
       </c>
       <c r="AY16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AZ16">
-        <v>476.4</v>
+        <v>478.1</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4378,286 +4366,286 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="CU1" s="1" t="s">
         <v>49</v>
@@ -4666,16 +4654,16 @@
         <v>48</v>
       </c>
       <c r="CW1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="CY1" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:104">
@@ -4692,22 +4680,22 @@
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F2" t="s">
         <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H2" t="s">
         <v>193</v>
       </c>
       <c r="I2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J2">
-        <v>553.8</v>
+        <v>555.5</v>
       </c>
       <c r="K2">
         <v>3.4</v>
@@ -4737,13 +4725,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="V2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="W2">
         <v>0.0833</v>
@@ -4833,10 +4821,10 @@
         <v>228.7</v>
       </c>
       <c r="AZ2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB2">
         <v>92.90000000000001</v>
@@ -4923,7 +4911,7 @@
         <v>1.1421</v>
       </c>
       <c r="CD2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE2">
         <v>2124</v>
@@ -5006,22 +4994,22 @@
         <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H3" t="s">
         <v>193</v>
       </c>
       <c r="I3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J3">
-        <v>553.8</v>
+        <v>555.5</v>
       </c>
       <c r="K3">
         <v>4.4</v>
@@ -5051,13 +5039,13 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="V3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="W3">
         <v>0.0833</v>
@@ -5147,10 +5135,10 @@
         <v>234.2</v>
       </c>
       <c r="AZ3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB3">
         <v>92.90000000000001</v>
@@ -5237,7 +5225,7 @@
         <v>1.1417</v>
       </c>
       <c r="CD3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE3">
         <v>2147</v>
@@ -5320,22 +5308,22 @@
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H4" t="s">
         <v>193</v>
       </c>
       <c r="I4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J4">
-        <v>553.8</v>
+        <v>555.5</v>
       </c>
       <c r="K4">
         <v>5.4</v>
@@ -5365,13 +5353,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
+        <v>362</v>
+      </c>
+      <c r="U4" t="s">
+        <v>365</v>
+      </c>
+      <c r="V4" t="s">
         <v>366</v>
-      </c>
-      <c r="U4" t="s">
-        <v>369</v>
-      </c>
-      <c r="V4" t="s">
-        <v>370</v>
       </c>
       <c r="W4">
         <v>0.0833</v>
@@ -5461,10 +5449,10 @@
         <v>233.7</v>
       </c>
       <c r="AZ4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB4">
         <v>91.90000000000001</v>
@@ -5551,7 +5539,7 @@
         <v>1.1428</v>
       </c>
       <c r="CD4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE4">
         <v>2115</v>
@@ -5634,22 +5622,22 @@
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F5" t="s">
         <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H5" t="s">
         <v>193</v>
       </c>
       <c r="I5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J5">
-        <v>553.8</v>
+        <v>555.5</v>
       </c>
       <c r="K5">
         <v>6.4</v>
@@ -5679,13 +5667,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
+        <v>362</v>
+      </c>
+      <c r="U5" t="s">
         <v>366</v>
       </c>
-      <c r="U5" t="s">
-        <v>370</v>
-      </c>
       <c r="V5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W5">
         <v>0.0833</v>
@@ -5712,7 +5700,7 @@
         <v>0.9</v>
       </c>
       <c r="AE5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AF5">
         <v>88.7</v>
@@ -5775,10 +5763,10 @@
         <v>237.2</v>
       </c>
       <c r="AZ5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB5">
         <v>89.90000000000001</v>
@@ -5865,7 +5853,7 @@
         <v>1.1448</v>
       </c>
       <c r="CD5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE5">
         <v>2052</v>
@@ -5948,25 +5936,25 @@
         <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F6" t="s">
         <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J6">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -5993,13 +5981,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="V6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="W6">
         <v>0.1667</v>
@@ -6089,10 +6077,10 @@
         <v>258</v>
       </c>
       <c r="AZ6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB6">
         <v>94.90000000000001</v>
@@ -6179,7 +6167,7 @@
         <v>1.1415</v>
       </c>
       <c r="CD6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE6">
         <v>2170</v>
@@ -6262,25 +6250,25 @@
         <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J7">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -6307,13 +6295,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
+        <v>362</v>
+      </c>
+      <c r="U7" t="s">
+        <v>365</v>
+      </c>
+      <c r="V7" t="s">
         <v>366</v>
-      </c>
-      <c r="U7" t="s">
-        <v>369</v>
-      </c>
-      <c r="V7" t="s">
-        <v>370</v>
       </c>
       <c r="W7">
         <v>0.1667</v>
@@ -6403,10 +6391,10 @@
         <v>258.6</v>
       </c>
       <c r="AZ7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB7">
         <v>94.7</v>
@@ -6493,7 +6481,7 @@
         <v>1.1431</v>
       </c>
       <c r="CD7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE7">
         <v>2117</v>
@@ -6576,25 +6564,25 @@
         <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J8">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="K8">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -6621,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
+        <v>362</v>
+      </c>
+      <c r="U8" t="s">
         <v>366</v>
       </c>
-      <c r="U8" t="s">
-        <v>370</v>
-      </c>
       <c r="V8" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W8">
         <v>0.1667</v>
@@ -6717,10 +6705,10 @@
         <v>258.3</v>
       </c>
       <c r="AZ8" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA8" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB8">
         <v>94.8</v>
@@ -6807,7 +6795,7 @@
         <v>1.1457</v>
       </c>
       <c r="CD8" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE8">
         <v>2034</v>
@@ -6890,25 +6878,25 @@
         <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G9" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J9">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="K9">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -6935,13 +6923,13 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V9" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W9">
         <v>0.1667</v>
@@ -6968,7 +6956,7 @@
         <v>0.6</v>
       </c>
       <c r="AE9" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AF9">
         <v>86.2</v>
@@ -7031,10 +7019,10 @@
         <v>256.5</v>
       </c>
       <c r="AZ9" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA9" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB9">
         <v>94.8</v>
@@ -7121,7 +7109,7 @@
         <v>1.149</v>
       </c>
       <c r="CD9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE9">
         <v>1929</v>
@@ -7204,25 +7192,25 @@
         <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F10" t="s">
         <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I10" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J10">
-        <v>445.2</v>
+        <v>446.8</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -7234,7 +7222,7 @@
         <v>0.9</v>
       </c>
       <c r="O10">
-        <v>10.31</v>
+        <v>11.42</v>
       </c>
       <c r="P10">
         <v>2.7</v>
@@ -7249,22 +7237,22 @@
         <v>100</v>
       </c>
       <c r="T10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U10" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="V10" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="W10">
         <v>0.1667</v>
       </c>
       <c r="X10">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>93.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="Z10">
         <v>53</v>
@@ -7306,7 +7294,7 @@
         <v>14.3</v>
       </c>
       <c r="AM10">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AN10">
         <v>0</v>
@@ -7345,10 +7333,10 @@
         <v>103.7</v>
       </c>
       <c r="AZ10" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA10" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB10">
         <v>96.7</v>
@@ -7435,7 +7423,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD10" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE10">
         <v>858</v>
@@ -7518,25 +7506,25 @@
         <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I11" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J11">
-        <v>445.2</v>
+        <v>446.8</v>
       </c>
       <c r="K11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -7548,7 +7536,7 @@
         <v>0.75</v>
       </c>
       <c r="O11">
-        <v>12.55</v>
+        <v>11.83</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -7563,22 +7551,22 @@
         <v>100</v>
       </c>
       <c r="T11" t="s">
+        <v>362</v>
+      </c>
+      <c r="U11" t="s">
+        <v>365</v>
+      </c>
+      <c r="V11" t="s">
         <v>366</v>
-      </c>
-      <c r="U11" t="s">
-        <v>369</v>
-      </c>
-      <c r="V11" t="s">
-        <v>370</v>
       </c>
       <c r="W11">
         <v>0.1667</v>
       </c>
       <c r="X11">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Y11">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="Z11">
         <v>53</v>
@@ -7620,7 +7608,7 @@
         <v>16.4</v>
       </c>
       <c r="AM11">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AN11">
         <v>0</v>
@@ -7659,10 +7647,10 @@
         <v>103.1</v>
       </c>
       <c r="AZ11" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA11" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB11">
         <v>97.7</v>
@@ -7749,7 +7737,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD11" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE11">
         <v>858</v>
@@ -7832,25 +7820,25 @@
         <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J12">
-        <v>445.2</v>
+        <v>446.8</v>
       </c>
       <c r="K12">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -7862,7 +7850,7 @@
         <v>0.21</v>
       </c>
       <c r="O12">
-        <v>14.24</v>
+        <v>13.2</v>
       </c>
       <c r="P12">
         <v>3.5</v>
@@ -7877,22 +7865,22 @@
         <v>100</v>
       </c>
       <c r="T12" t="s">
+        <v>362</v>
+      </c>
+      <c r="U12" t="s">
         <v>366</v>
       </c>
-      <c r="U12" t="s">
-        <v>370</v>
-      </c>
       <c r="V12" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W12">
         <v>0.1667</v>
       </c>
       <c r="X12">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="Y12">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="Z12">
         <v>53</v>
@@ -7934,7 +7922,7 @@
         <v>25.4</v>
       </c>
       <c r="AM12">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AN12">
         <v>0.001</v>
@@ -7967,16 +7955,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AY12">
         <v>99.7</v>
       </c>
       <c r="AZ12" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA12" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB12">
         <v>97.3</v>
@@ -8063,7 +8051,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD12" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE12">
         <v>858</v>
@@ -8146,25 +8134,25 @@
         <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G13" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I13" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J13">
-        <v>445.2</v>
+        <v>446.8</v>
       </c>
       <c r="K13">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -8176,7 +8164,7 @@
         <v>1.34</v>
       </c>
       <c r="O13">
-        <v>15.97</v>
+        <v>14.79</v>
       </c>
       <c r="P13">
         <v>4.3</v>
@@ -8191,22 +8179,22 @@
         <v>100</v>
       </c>
       <c r="T13" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U13" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V13" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W13">
         <v>0.1667</v>
       </c>
       <c r="X13">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="Y13">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z13">
         <v>45.8</v>
@@ -8248,7 +8236,7 @@
         <v>31.9</v>
       </c>
       <c r="AM13">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="AN13">
         <v>0.002</v>
@@ -8281,16 +8269,16 @@
         <v>4.8</v>
       </c>
       <c r="AX13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AY13">
         <v>95.3</v>
       </c>
       <c r="AZ13" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA13" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB13">
         <v>96.3</v>
@@ -8377,7 +8365,7 @@
         <v>1.1575</v>
       </c>
       <c r="CD13" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE13">
         <v>1586</v>
@@ -8422,7 +8410,7 @@
         <v>48.7</v>
       </c>
       <c r="CS13">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="CT13" t="s">
         <v>190</v>
@@ -8460,22 +8448,22 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F14" t="s">
         <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I14" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J14">
-        <v>453.6</v>
+        <v>455.3</v>
       </c>
       <c r="K14">
         <v>6.4</v>
@@ -8490,7 +8478,7 @@
         <v>1.59</v>
       </c>
       <c r="O14">
-        <v>5.02</v>
+        <v>5.39</v>
       </c>
       <c r="P14">
         <v>6.3</v>
@@ -8505,19 +8493,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
+        <v>362</v>
+      </c>
+      <c r="U14" t="s">
         <v>366</v>
       </c>
-      <c r="U14" t="s">
-        <v>370</v>
-      </c>
       <c r="V14" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W14">
         <v>0.0833</v>
       </c>
       <c r="X14">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="Y14">
         <v>86.09999999999999</v>
@@ -8562,7 +8550,7 @@
         <v>56.4</v>
       </c>
       <c r="AM14">
-        <v>30.9</v>
+        <v>29.5</v>
       </c>
       <c r="AN14">
         <v>0.001</v>
@@ -8601,10 +8589,10 @@
         <v>251.2</v>
       </c>
       <c r="AZ14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="BA14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="BB14">
         <v>90.90000000000001</v>
@@ -8691,7 +8679,7 @@
         <v>1.1455</v>
       </c>
       <c r="CD14" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE14">
         <v>2024</v>
@@ -8736,7 +8724,7 @@
         <v>43.6</v>
       </c>
       <c r="CS14">
-        <v>29.4</v>
+        <v>28.7</v>
       </c>
       <c r="CT14" t="s">
         <v>189</v>
@@ -8774,22 +8762,22 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G15" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I15" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J15">
-        <v>453.6</v>
+        <v>455.3</v>
       </c>
       <c r="K15">
         <v>7.4</v>
@@ -8804,7 +8792,7 @@
         <v>1.42</v>
       </c>
       <c r="O15">
-        <v>9.4</v>
+        <v>7.18</v>
       </c>
       <c r="P15">
         <v>23.9</v>
@@ -8819,25 +8807,25 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V15" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W15">
         <v>0.0833</v>
       </c>
       <c r="X15">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="Y15">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="Z15">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="AA15">
         <v>0.98</v>
@@ -8876,7 +8864,7 @@
         <v>51</v>
       </c>
       <c r="AM15">
-        <v>28.4</v>
+        <v>29</v>
       </c>
       <c r="AN15">
         <v>0.002</v>
@@ -8915,10 +8903,10 @@
         <v>234.2</v>
       </c>
       <c r="AZ15" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="BA15" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="BB15">
         <v>77.59999999999999</v>
@@ -9005,7 +8993,7 @@
         <v>1.1491</v>
       </c>
       <c r="CD15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE15">
         <v>1904</v>
@@ -9050,7 +9038,7 @@
         <v>46</v>
       </c>
       <c r="CS15">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="CT15" t="s">
         <v>189</v>
@@ -9088,22 +9076,22 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G16" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I16" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J16">
-        <v>453.6</v>
+        <v>455.3</v>
       </c>
       <c r="K16">
         <v>8.4</v>
@@ -9118,7 +9106,7 @@
         <v>1.81</v>
       </c>
       <c r="O16">
-        <v>9.199999999999999</v>
+        <v>6.13</v>
       </c>
       <c r="P16">
         <v>32.2</v>
@@ -9133,25 +9121,25 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U16" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V16" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W16">
         <v>0.0833</v>
       </c>
       <c r="X16">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="Y16">
-        <v>85.7</v>
+        <v>86.2</v>
       </c>
       <c r="Z16">
-        <v>69.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="AA16">
         <v>0.98</v>
@@ -9166,7 +9154,7 @@
         <v>1.6</v>
       </c>
       <c r="AE16" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="AF16">
         <v>85.09999999999999</v>
@@ -9190,7 +9178,7 @@
         <v>84.90000000000001</v>
       </c>
       <c r="AM16">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="AN16">
         <v>0.001</v>
@@ -9229,10 +9217,10 @@
         <v>229.1</v>
       </c>
       <c r="AZ16" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA16" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB16">
         <v>73.2</v>
@@ -9319,7 +9307,7 @@
         <v>1.154</v>
       </c>
       <c r="CD16" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE16">
         <v>1745</v>
@@ -9364,7 +9352,7 @@
         <v>50.9</v>
       </c>
       <c r="CS16">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="CT16" t="s">
         <v>189</v>
@@ -9402,22 +9390,22 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G17" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I17" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J17">
-        <v>453.6</v>
+        <v>455.3</v>
       </c>
       <c r="K17">
         <v>9.4</v>
@@ -9432,7 +9420,7 @@
         <v>1.04</v>
       </c>
       <c r="O17">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="P17">
         <v>22.2</v>
@@ -9447,19 +9435,19 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U17" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V17" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W17">
         <v>0.0833</v>
       </c>
       <c r="X17">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y17">
         <v>92.2</v>
@@ -9543,10 +9531,10 @@
         <v>230.7</v>
       </c>
       <c r="AZ17" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA17" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB17">
         <v>81.3</v>
@@ -9633,7 +9621,7 @@
         <v>1.1599</v>
       </c>
       <c r="CD17" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE17">
         <v>1564</v>
@@ -9716,25 +9704,25 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F18" t="s">
         <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I18" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J18">
-        <v>150.7</v>
+        <v>152.3</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -9746,7 +9734,7 @@
         <v>0.71</v>
       </c>
       <c r="O18">
-        <v>24.7</v>
+        <v>24.37</v>
       </c>
       <c r="P18">
         <v>9.1</v>
@@ -9761,22 +9749,22 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
+        <v>362</v>
+      </c>
+      <c r="U18" t="s">
         <v>366</v>
       </c>
-      <c r="U18" t="s">
-        <v>370</v>
-      </c>
       <c r="V18" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W18">
         <v>0.6667</v>
       </c>
       <c r="X18">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y18">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z18">
         <v>60</v>
@@ -9818,7 +9806,7 @@
         <v>14.3</v>
       </c>
       <c r="AM18">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="AN18">
         <v>0.005</v>
@@ -9857,10 +9845,10 @@
         <v>224.7</v>
       </c>
       <c r="AZ18" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA18" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB18">
         <v>91.7</v>
@@ -9947,7 +9935,7 @@
         <v>1.1255</v>
       </c>
       <c r="CD18" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE18">
         <v>2584</v>
@@ -9992,7 +9980,7 @@
         <v>53.6</v>
       </c>
       <c r="CS18">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="CT18" t="s">
         <v>189</v>
@@ -10030,25 +10018,25 @@
         <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G19" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I19" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J19">
-        <v>150.7</v>
+        <v>152.3</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -10060,7 +10048,7 @@
         <v>1.31</v>
       </c>
       <c r="O19">
-        <v>28.83</v>
+        <v>29.44</v>
       </c>
       <c r="P19">
         <v>12.1</v>
@@ -10075,22 +10063,22 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U19" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V19" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W19">
         <v>0.6667</v>
       </c>
       <c r="X19">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="Y19">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="Z19">
         <v>58.5</v>
@@ -10132,7 +10120,7 @@
         <v>14.1</v>
       </c>
       <c r="AM19">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="AN19">
         <v>0.005</v>
@@ -10171,10 +10159,10 @@
         <v>216.3</v>
       </c>
       <c r="AZ19" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA19" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB19">
         <v>91.2</v>
@@ -10261,7 +10249,7 @@
         <v>1.131</v>
       </c>
       <c r="CD19" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE19">
         <v>2415</v>
@@ -10306,7 +10294,7 @@
         <v>56.4</v>
       </c>
       <c r="CS19">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="CT19" t="s">
         <v>189</v>
@@ -10344,25 +10332,25 @@
         <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F20" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G20" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I20" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J20">
-        <v>150.7</v>
+        <v>152.3</v>
       </c>
       <c r="K20">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -10374,7 +10362,7 @@
         <v>0.63</v>
       </c>
       <c r="O20">
-        <v>26.82</v>
+        <v>27.33</v>
       </c>
       <c r="P20">
         <v>16.2</v>
@@ -10389,22 +10377,22 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U20" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V20" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W20">
         <v>0.6667</v>
       </c>
       <c r="X20">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="Y20">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="Z20">
         <v>58.1</v>
@@ -10422,7 +10410,7 @@
         <v>0.2</v>
       </c>
       <c r="AE20" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AF20">
         <v>77.5</v>
@@ -10446,7 +10434,7 @@
         <v>15.7</v>
       </c>
       <c r="AM20">
-        <v>29.8</v>
+        <v>29.4</v>
       </c>
       <c r="AN20">
         <v>0.01</v>
@@ -10485,10 +10473,10 @@
         <v>224.5</v>
       </c>
       <c r="AZ20" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA20" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB20">
         <v>90.2</v>
@@ -10575,7 +10563,7 @@
         <v>1.1372</v>
       </c>
       <c r="CD20" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE20">
         <v>2227</v>
@@ -10620,7 +10608,7 @@
         <v>61.7</v>
       </c>
       <c r="CS20">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="CT20" t="s">
         <v>189</v>
@@ -10658,25 +10646,25 @@
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I21" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J21">
-        <v>150.7</v>
+        <v>152.3</v>
       </c>
       <c r="K21">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -10688,7 +10676,7 @@
         <v>0.45</v>
       </c>
       <c r="O21">
-        <v>20.69</v>
+        <v>21.34</v>
       </c>
       <c r="P21">
         <v>26.8</v>
@@ -10703,25 +10691,25 @@
         <v>25</v>
       </c>
       <c r="T21" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U21" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V21" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W21">
         <v>0.6667</v>
       </c>
       <c r="X21">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="Y21">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z21">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="AA21">
         <v>0.92</v>
@@ -10736,7 +10724,7 @@
         <v>0.2</v>
       </c>
       <c r="AE21" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AF21">
         <v>75.5</v>
@@ -10760,7 +10748,7 @@
         <v>23.4</v>
       </c>
       <c r="AM21">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="AN21">
         <v>0.013</v>
@@ -10799,10 +10787,10 @@
         <v>221.7</v>
       </c>
       <c r="AZ21" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA21" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB21">
         <v>83.40000000000001</v>
@@ -10889,7 +10877,7 @@
         <v>1.1422</v>
       </c>
       <c r="CD21" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE21">
         <v>2075</v>
@@ -10934,7 +10922,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="CS21">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="CT21" t="s">
         <v>189</v>
@@ -10972,22 +10960,22 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F22" t="s">
         <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I22" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J22">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="K22">
         <v>7</v>
@@ -11002,7 +10990,7 @@
         <v>0.8</v>
       </c>
       <c r="O22">
-        <v>6.87</v>
+        <v>6.84</v>
       </c>
       <c r="P22">
         <v>21.4</v>
@@ -11017,13 +11005,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
+        <v>362</v>
+      </c>
+      <c r="U22" t="s">
         <v>366</v>
       </c>
-      <c r="U22" t="s">
-        <v>370</v>
-      </c>
       <c r="V22" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W22">
         <v>0.75</v>
@@ -11074,7 +11062,7 @@
         <v>93.8</v>
       </c>
       <c r="AM22">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AN22">
         <v>0.002</v>
@@ -11113,10 +11101,10 @@
         <v>234.3</v>
       </c>
       <c r="AZ22" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA22" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB22">
         <v>84.8</v>
@@ -11203,7 +11191,7 @@
         <v>1.1525</v>
       </c>
       <c r="CD22" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE22">
         <v>1788</v>
@@ -11248,7 +11236,7 @@
         <v>52</v>
       </c>
       <c r="CS22">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="CT22" t="s">
         <v>189</v>
@@ -11286,22 +11274,22 @@
         <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F23" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G23" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I23" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J23">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="K23">
         <v>8</v>
@@ -11316,7 +11304,7 @@
         <v>1.35</v>
       </c>
       <c r="O23">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="P23">
         <v>25.7</v>
@@ -11331,22 +11319,22 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U23" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V23" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W23">
         <v>0.75</v>
       </c>
       <c r="X23">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Y23">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="Z23">
         <v>64.7</v>
@@ -11364,7 +11352,7 @@
         <v>0.5</v>
       </c>
       <c r="AE23" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AF23">
         <v>82.3</v>
@@ -11388,7 +11376,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="AM23">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AN23">
         <v>0.02</v>
@@ -11427,10 +11415,10 @@
         <v>221.7</v>
       </c>
       <c r="AZ23" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BA23" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="BB23">
         <v>80.40000000000001</v>
@@ -11517,7 +11505,7 @@
         <v>1.1591</v>
       </c>
       <c r="CD23" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE23">
         <v>1587</v>
@@ -11562,7 +11550,7 @@
         <v>55.5</v>
       </c>
       <c r="CS23">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="CT23" t="s">
         <v>189</v>
@@ -11600,22 +11588,22 @@
         <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F24" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G24" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I24" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J24">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -11645,13 +11633,13 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U24" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V24" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W24">
         <v>0.75</v>
@@ -11735,16 +11723,16 @@
         <v>7.1</v>
       </c>
       <c r="AX24" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AY24">
         <v>208</v>
       </c>
       <c r="AZ24" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="BA24" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="BB24">
         <v>89.8</v>
@@ -11831,7 +11819,7 @@
         <v>1.1638</v>
       </c>
       <c r="CD24" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE24">
         <v>1450</v>
@@ -11914,22 +11902,22 @@
         <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F25" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G25" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I25" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J25">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="K25">
         <v>10</v>
@@ -11944,7 +11932,7 @@
         <v>2.38</v>
       </c>
       <c r="O25">
-        <v>0.38</v>
+        <v>2.4</v>
       </c>
       <c r="P25">
         <v>10.5</v>
@@ -11959,22 +11947,22 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U25" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V25" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W25">
         <v>0.75</v>
       </c>
       <c r="X25">
-        <v>23.8</v>
+        <v>24.5</v>
       </c>
       <c r="Y25">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="Z25">
         <v>64.5</v>
@@ -12049,16 +12037,16 @@
         <v>5.5</v>
       </c>
       <c r="AX25" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AY25">
         <v>198.3</v>
       </c>
       <c r="AZ25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="BA25" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="BB25">
         <v>87.5</v>
@@ -12145,7 +12133,7 @@
         <v>1.1656</v>
       </c>
       <c r="CD25" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE25">
         <v>1399</v>
@@ -12228,25 +12216,25 @@
         <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F26" t="s">
         <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I26" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J26">
-        <v>500.6</v>
+        <v>502.3</v>
       </c>
       <c r="K26">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -12258,7 +12246,7 @@
         <v>0.6</v>
       </c>
       <c r="O26">
-        <v>1.16</v>
+        <v>0.32</v>
       </c>
       <c r="P26">
         <v>11.7</v>
@@ -12273,22 +12261,22 @@
         <v>56.2</v>
       </c>
       <c r="T26" t="s">
+        <v>362</v>
+      </c>
+      <c r="U26" t="s">
         <v>366</v>
       </c>
-      <c r="U26" t="s">
-        <v>370</v>
-      </c>
       <c r="V26" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W26">
         <v>0.1667</v>
       </c>
       <c r="X26">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y26">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="Z26">
         <v>60.3</v>
@@ -12330,7 +12318,7 @@
         <v>13.7</v>
       </c>
       <c r="AM26">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AN26">
         <v>0</v>
@@ -12369,10 +12357,10 @@
         <v>132.5</v>
       </c>
       <c r="AZ26" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA26" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB26">
         <v>91.40000000000001</v>
@@ -12459,7 +12447,7 @@
         <v>1.1099</v>
       </c>
       <c r="CD26" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE26">
         <v>3104</v>
@@ -12504,7 +12492,7 @@
         <v>48.6</v>
       </c>
       <c r="CS26">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="CT26" t="s">
         <v>190</v>
@@ -12542,25 +12530,25 @@
         <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F27" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G27" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H27" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I27" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J27">
-        <v>500.6</v>
+        <v>502.3</v>
       </c>
       <c r="K27">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -12572,7 +12560,7 @@
         <v>0.84</v>
       </c>
       <c r="O27">
-        <v>1.09</v>
+        <v>0.41</v>
       </c>
       <c r="P27">
         <v>13</v>
@@ -12587,22 +12575,22 @@
         <v>56.2</v>
       </c>
       <c r="T27" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U27" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V27" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W27">
         <v>0.1667</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Y27">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Z27">
         <v>60</v>
@@ -12644,7 +12632,7 @@
         <v>18.3</v>
       </c>
       <c r="AM27">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AN27">
         <v>0</v>
@@ -12683,10 +12671,10 @@
         <v>131.1</v>
       </c>
       <c r="AZ27" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA27" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB27">
         <v>90.09999999999999</v>
@@ -12773,7 +12761,7 @@
         <v>1.1112</v>
       </c>
       <c r="CD27" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE27">
         <v>3048</v>
@@ -12818,7 +12806,7 @@
         <v>48</v>
       </c>
       <c r="CS27">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="CT27" t="s">
         <v>190</v>
@@ -12856,25 +12844,25 @@
         <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F28" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G28" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I28" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J28">
-        <v>500.6</v>
+        <v>502.3</v>
       </c>
       <c r="K28">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -12901,13 +12889,13 @@
         <v>56.2</v>
       </c>
       <c r="T28" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U28" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V28" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W28">
         <v>0.1667</v>
@@ -12997,10 +12985,10 @@
         <v>129.9</v>
       </c>
       <c r="AZ28" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA28" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB28">
         <v>90</v>
@@ -13087,7 +13075,7 @@
         <v>1.1159</v>
       </c>
       <c r="CD28" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE28">
         <v>2899</v>
@@ -13170,25 +13158,25 @@
         <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F29" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G29" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I29" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J29">
-        <v>500.6</v>
+        <v>502.3</v>
       </c>
       <c r="K29">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -13200,7 +13188,7 @@
         <v>1.43</v>
       </c>
       <c r="O29">
-        <v>3.34</v>
+        <v>0.5</v>
       </c>
       <c r="P29">
         <v>11.1</v>
@@ -13215,22 +13203,22 @@
         <v>18.8</v>
       </c>
       <c r="T29" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U29" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V29" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W29">
         <v>0.1667</v>
       </c>
       <c r="X29">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y29">
-        <v>93.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="Z29">
         <v>59.2</v>
@@ -13272,7 +13260,7 @@
         <v>15.4</v>
       </c>
       <c r="AM29">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="AN29">
         <v>0</v>
@@ -13311,10 +13299,10 @@
         <v>133.2</v>
       </c>
       <c r="AZ29" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA29" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB29">
         <v>92.09999999999999</v>
@@ -13401,7 +13389,7 @@
         <v>1.1213</v>
       </c>
       <c r="CD29" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE29">
         <v>2734</v>
@@ -13446,7 +13434,7 @@
         <v>54.7</v>
       </c>
       <c r="CS29">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="CT29" t="s">
         <v>190</v>
@@ -13484,25 +13472,25 @@
         <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F30" t="s">
         <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I30" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J30">
-        <v>70.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K30">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -13529,13 +13517,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
+        <v>362</v>
+      </c>
+      <c r="U30" t="s">
         <v>366</v>
       </c>
-      <c r="U30" t="s">
-        <v>370</v>
-      </c>
       <c r="V30" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W30">
         <v>0.1667</v>
@@ -13625,10 +13613,10 @@
         <v>273.6</v>
       </c>
       <c r="AZ30" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA30" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB30">
         <v>98.2</v>
@@ -13715,7 +13703,7 @@
         <v>1.1423</v>
       </c>
       <c r="CD30" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE30">
         <v>2223</v>
@@ -13798,25 +13786,25 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F31" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G31" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I31" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J31">
-        <v>70.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K31">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -13843,13 +13831,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U31" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V31" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W31">
         <v>0.1667</v>
@@ -13939,10 +13927,10 @@
         <v>264.6</v>
       </c>
       <c r="AZ31" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BA31" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BB31">
         <v>94.90000000000001</v>
@@ -14029,7 +14017,7 @@
         <v>1.145</v>
       </c>
       <c r="CD31" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE31">
         <v>2135</v>
@@ -14112,25 +14100,25 @@
         <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F32" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G32" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H32" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I32" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J32">
-        <v>70.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K32">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -14157,13 +14145,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U32" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V32" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W32">
         <v>0.1667</v>
@@ -14253,10 +14241,10 @@
         <v>244.7</v>
       </c>
       <c r="AZ32" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BA32" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BB32">
         <v>95.09999999999999</v>
@@ -14343,7 +14331,7 @@
         <v>1.1508</v>
       </c>
       <c r="CD32" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE32">
         <v>1951</v>
@@ -14426,25 +14414,25 @@
         <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F33" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G33" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I33" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J33">
-        <v>70.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K33">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -14471,13 +14459,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U33" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V33" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W33">
         <v>0.1667</v>
@@ -14567,10 +14555,10 @@
         <v>226.9</v>
       </c>
       <c r="AZ33" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA33" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB33">
         <v>86.5</v>
@@ -14657,7 +14645,7 @@
         <v>1.1571</v>
       </c>
       <c r="CD33" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE33">
         <v>1755</v>
@@ -14740,22 +14728,22 @@
         <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F34" t="s">
         <v>114</v>
       </c>
       <c r="G34" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H34" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J34">
-        <v>525.3</v>
+        <v>527</v>
       </c>
       <c r="K34">
         <v>7.5</v>
@@ -14785,13 +14773,13 @@
         <v>81.2</v>
       </c>
       <c r="T34" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U34" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="V34" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="W34">
         <v>0.25</v>
@@ -14881,10 +14869,10 @@
         <v>289.7</v>
       </c>
       <c r="AZ34" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BA34" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BB34">
         <v>89.59999999999999</v>
@@ -14971,7 +14959,7 @@
         <v>1.165</v>
       </c>
       <c r="CD34" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE34">
         <v>1454</v>
@@ -15054,22 +15042,22 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G35" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I35" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J35">
-        <v>525.3</v>
+        <v>527</v>
       </c>
       <c r="K35">
         <v>8.5</v>
@@ -15099,13 +15087,13 @@
         <v>81.2</v>
       </c>
       <c r="T35" t="s">
+        <v>362</v>
+      </c>
+      <c r="U35" t="s">
+        <v>365</v>
+      </c>
+      <c r="V35" t="s">
         <v>366</v>
-      </c>
-      <c r="U35" t="s">
-        <v>369</v>
-      </c>
-      <c r="V35" t="s">
-        <v>370</v>
       </c>
       <c r="W35">
         <v>0.25</v>
@@ -15195,10 +15183,10 @@
         <v>290</v>
       </c>
       <c r="AZ35" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BA35" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BB35">
         <v>87.5</v>
@@ -15285,7 +15273,7 @@
         <v>1.1673</v>
       </c>
       <c r="CD35" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE35">
         <v>1386</v>
@@ -15368,22 +15356,22 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F36" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G36" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J36">
-        <v>525.3</v>
+        <v>527</v>
       </c>
       <c r="K36">
         <v>9.5</v>
@@ -15413,13 +15401,13 @@
         <v>56.2</v>
       </c>
       <c r="T36" t="s">
+        <v>362</v>
+      </c>
+      <c r="U36" t="s">
         <v>366</v>
       </c>
-      <c r="U36" t="s">
-        <v>370</v>
-      </c>
       <c r="V36" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W36">
         <v>0.25</v>
@@ -15509,10 +15497,10 @@
         <v>288.8</v>
       </c>
       <c r="AZ36" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BA36" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BB36">
         <v>87.40000000000001</v>
@@ -15599,7 +15587,7 @@
         <v>1.1704</v>
       </c>
       <c r="CD36" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE36">
         <v>1299</v>
@@ -15682,22 +15670,22 @@
         <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F37" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G37" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J37">
-        <v>525.3</v>
+        <v>527</v>
       </c>
       <c r="K37">
         <v>10.5</v>
@@ -15727,13 +15715,13 @@
         <v>81.2</v>
       </c>
       <c r="T37" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U37" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V37" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W37">
         <v>0.25</v>
@@ -15817,16 +15805,16 @@
         <v>4.1</v>
       </c>
       <c r="AX37" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AY37">
         <v>308.9</v>
       </c>
       <c r="AZ37" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BA37" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BB37">
         <v>89.3</v>
@@ -15913,7 +15901,7 @@
         <v>1.1757</v>
       </c>
       <c r="CD37" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE37">
         <v>1141</v>
@@ -15996,22 +15984,22 @@
         <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F38" t="s">
         <v>114</v>
       </c>
       <c r="G38" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I38" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J38">
-        <v>410.1</v>
+        <v>411.8</v>
       </c>
       <c r="K38">
         <v>7.5</v>
@@ -16041,13 +16029,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U38" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="V38" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="W38">
         <v>0.25</v>
@@ -16137,10 +16125,10 @@
         <v>243.8</v>
       </c>
       <c r="AZ38" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA38" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB38">
         <v>91.7</v>
@@ -16227,7 +16215,7 @@
         <v>1.2159</v>
       </c>
       <c r="CD38" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE38">
         <v>64</v>
@@ -16310,22 +16298,22 @@
         <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F39" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G39" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I39" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J39">
-        <v>410.1</v>
+        <v>411.8</v>
       </c>
       <c r="K39">
         <v>8.5</v>
@@ -16355,13 +16343,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
+        <v>362</v>
+      </c>
+      <c r="U39" t="s">
+        <v>365</v>
+      </c>
+      <c r="V39" t="s">
         <v>366</v>
-      </c>
-      <c r="U39" t="s">
-        <v>369</v>
-      </c>
-      <c r="V39" t="s">
-        <v>370</v>
       </c>
       <c r="W39">
         <v>0.25</v>
@@ -16451,10 +16439,10 @@
         <v>238.2</v>
       </c>
       <c r="AZ39" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA39" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB39">
         <v>84</v>
@@ -16541,7 +16529,7 @@
         <v>1.2148</v>
       </c>
       <c r="CD39" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE39">
         <v>91</v>
@@ -16624,22 +16612,22 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F40" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G40" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I40" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J40">
-        <v>410.1</v>
+        <v>411.8</v>
       </c>
       <c r="K40">
         <v>9.5</v>
@@ -16669,13 +16657,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
+        <v>362</v>
+      </c>
+      <c r="U40" t="s">
         <v>366</v>
       </c>
-      <c r="U40" t="s">
-        <v>370</v>
-      </c>
       <c r="V40" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W40">
         <v>0.25</v>
@@ -16765,10 +16753,10 @@
         <v>229.3</v>
       </c>
       <c r="AZ40" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA40" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB40">
         <v>77.59999999999999</v>
@@ -16855,7 +16843,7 @@
         <v>1.2164</v>
       </c>
       <c r="CD40" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE40">
         <v>47</v>
@@ -16938,22 +16926,22 @@
         <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F41" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G41" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I41" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J41">
-        <v>410.1</v>
+        <v>411.8</v>
       </c>
       <c r="K41">
         <v>10.5</v>
@@ -16983,13 +16971,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U41" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V41" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W41">
         <v>0.25</v>
@@ -17073,16 +17061,16 @@
         <v>8.6</v>
       </c>
       <c r="AX41" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AY41">
         <v>213.6</v>
       </c>
       <c r="AZ41" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BA41" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BB41">
         <v>77.3</v>
@@ -17169,7 +17157,7 @@
         <v>1.218</v>
       </c>
       <c r="CD41" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE41">
         <v>-0</v>
@@ -17252,22 +17240,22 @@
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F42" t="s">
         <v>115</v>
       </c>
       <c r="G42" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I42" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J42">
-        <v>245.8</v>
+        <v>247.5</v>
       </c>
       <c r="K42">
         <v>7.5</v>
@@ -17282,7 +17270,7 @@
         <v>2.42</v>
       </c>
       <c r="O42">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="P42">
         <v>9.699999999999999</v>
@@ -17297,22 +17285,22 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
+        <v>362</v>
+      </c>
+      <c r="U42" t="s">
         <v>366</v>
       </c>
-      <c r="U42" t="s">
-        <v>370</v>
-      </c>
       <c r="V42" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W42">
         <v>0.25</v>
       </c>
       <c r="X42">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="Y42">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z42">
         <v>58.7</v>
@@ -17354,7 +17342,7 @@
         <v>13.4</v>
       </c>
       <c r="AM42">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AN42">
         <v>0</v>
@@ -17393,10 +17381,10 @@
         <v>159.1</v>
       </c>
       <c r="AZ42" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA42" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB42">
         <v>92.90000000000001</v>
@@ -17483,7 +17471,7 @@
         <v>1.1306</v>
       </c>
       <c r="CD42" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE42">
         <v>2463</v>
@@ -17528,7 +17516,7 @@
         <v>47.8</v>
       </c>
       <c r="CS42">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="CT42" t="s">
         <v>190</v>
@@ -17566,22 +17554,22 @@
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F43" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G43" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I43" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J43">
-        <v>245.8</v>
+        <v>247.5</v>
       </c>
       <c r="K43">
         <v>8.5</v>
@@ -17611,13 +17599,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U43" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V43" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W43">
         <v>0.25</v>
@@ -17707,10 +17695,10 @@
         <v>154.3</v>
       </c>
       <c r="AZ43" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA43" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB43">
         <v>89.8</v>
@@ -17797,7 +17785,7 @@
         <v>1.1332</v>
       </c>
       <c r="CD43" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE43">
         <v>2365</v>
@@ -17880,22 +17868,22 @@
         <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G44" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I44" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J44">
-        <v>245.8</v>
+        <v>247.5</v>
       </c>
       <c r="K44">
         <v>9.5</v>
@@ -17925,13 +17913,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U44" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V44" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W44">
         <v>0.25</v>
@@ -18021,10 +18009,10 @@
         <v>144.2</v>
       </c>
       <c r="AZ44" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA44" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB44">
         <v>79.5</v>
@@ -18111,7 +18099,7 @@
         <v>1.1388</v>
       </c>
       <c r="CD44" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE44">
         <v>2181</v>
@@ -18194,22 +18182,22 @@
         <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G45" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I45" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J45">
-        <v>245.8</v>
+        <v>247.5</v>
       </c>
       <c r="K45">
         <v>10.5</v>
@@ -18239,13 +18227,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U45" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V45" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W45">
         <v>0.25</v>
@@ -18335,10 +18323,10 @@
         <v>142.6</v>
       </c>
       <c r="AZ45" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA45" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB45">
         <v>82.40000000000001</v>
@@ -18425,7 +18413,7 @@
         <v>1.1454</v>
       </c>
       <c r="CD45" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE45">
         <v>1973</v>
@@ -18508,22 +18496,22 @@
         <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F46" t="s">
         <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I46" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J46">
-        <v>165.2</v>
+        <v>166.9</v>
       </c>
       <c r="K46">
         <v>7.5</v>
@@ -18538,7 +18526,7 @@
         <v>1.14</v>
       </c>
       <c r="O46">
-        <v>13.42</v>
+        <v>13.56</v>
       </c>
       <c r="P46">
         <v>15</v>
@@ -18553,19 +18541,19 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
+        <v>362</v>
+      </c>
+      <c r="U46" t="s">
         <v>366</v>
       </c>
-      <c r="U46" t="s">
-        <v>370</v>
-      </c>
       <c r="V46" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W46">
         <v>0.25</v>
       </c>
       <c r="X46">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="Y46">
         <v>92.09999999999999</v>
@@ -18610,7 +18598,7 @@
         <v>30.1</v>
       </c>
       <c r="AM46">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="AN46">
         <v>0.001</v>
@@ -18649,10 +18637,10 @@
         <v>158.2</v>
       </c>
       <c r="AZ46" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BA46" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BB46">
         <v>88.09999999999999</v>
@@ -18739,7 +18727,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD46" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE46">
         <v>858</v>
@@ -18822,22 +18810,22 @@
         <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F47" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G47" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I47" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J47">
-        <v>165.2</v>
+        <v>166.9</v>
       </c>
       <c r="K47">
         <v>8.5</v>
@@ -18852,7 +18840,7 @@
         <v>0.79</v>
       </c>
       <c r="O47">
-        <v>13.18</v>
+        <v>12.67</v>
       </c>
       <c r="P47">
         <v>13</v>
@@ -18867,22 +18855,22 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U47" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V47" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W47">
         <v>0.25</v>
       </c>
       <c r="X47">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y47">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z47">
         <v>53.3</v>
@@ -18924,7 +18912,7 @@
         <v>10.1</v>
       </c>
       <c r="AM47">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="AN47">
         <v>0</v>
@@ -18963,10 +18951,10 @@
         <v>159.1</v>
       </c>
       <c r="AZ47" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BA47" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BB47">
         <v>89.2</v>
@@ -19053,7 +19041,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD47" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE47">
         <v>858</v>
@@ -19136,22 +19124,22 @@
         <v>129</v>
       </c>
       <c r="E48" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F48" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G48" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H48" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I48" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J48">
-        <v>165.2</v>
+        <v>166.9</v>
       </c>
       <c r="K48">
         <v>9.5</v>
@@ -19181,13 +19169,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U48" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V48" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W48">
         <v>0.25</v>
@@ -19277,10 +19265,10 @@
         <v>151.8</v>
       </c>
       <c r="AZ48" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BA48" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BB48">
         <v>83.59999999999999</v>
@@ -19367,7 +19355,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD48" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE48">
         <v>858</v>
@@ -19450,22 +19438,22 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F49" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G49" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H49" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J49">
-        <v>165.2</v>
+        <v>166.9</v>
       </c>
       <c r="K49">
         <v>10.5</v>
@@ -19495,13 +19483,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U49" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V49" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W49">
         <v>0.25</v>
@@ -19585,16 +19573,16 @@
         <v>0</v>
       </c>
       <c r="AX49" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="AY49">
         <v>173.9</v>
       </c>
       <c r="AZ49" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BA49" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BB49">
         <v>84.59999999999999</v>
@@ -19681,7 +19669,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD49" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE49">
         <v>858</v>
@@ -19764,22 +19752,22 @@
         <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F50" t="s">
         <v>115</v>
       </c>
       <c r="G50" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I50" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J50">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K50">
         <v>7.5</v>
@@ -19809,13 +19797,13 @@
         <v>75</v>
       </c>
       <c r="T50" t="s">
+        <v>362</v>
+      </c>
+      <c r="U50" t="s">
         <v>366</v>
       </c>
-      <c r="U50" t="s">
-        <v>370</v>
-      </c>
       <c r="V50" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W50">
         <v>0.25</v>
@@ -19905,10 +19893,10 @@
         <v>108.4</v>
       </c>
       <c r="AZ50" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA50" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB50">
         <v>45.9</v>
@@ -19995,7 +19983,7 @@
         <v>1.1491</v>
       </c>
       <c r="CD50" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE50">
         <v>1947</v>
@@ -20078,22 +20066,22 @@
         <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F51" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G51" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I51" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J51">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K51">
         <v>8.5</v>
@@ -20123,13 +20111,13 @@
         <v>75</v>
       </c>
       <c r="T51" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U51" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V51" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W51">
         <v>0.25</v>
@@ -20219,10 +20207,10 @@
         <v>109.8</v>
       </c>
       <c r="AZ51" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA51" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB51">
         <v>47.3</v>
@@ -20309,7 +20297,7 @@
         <v>1.1525</v>
       </c>
       <c r="CD51" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE51">
         <v>1839</v>
@@ -20392,22 +20380,22 @@
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F52" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G52" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I52" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J52">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K52">
         <v>9.5</v>
@@ -20437,13 +20425,13 @@
         <v>75</v>
       </c>
       <c r="T52" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U52" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V52" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W52">
         <v>0.25</v>
@@ -20533,10 +20521,10 @@
         <v>115.2</v>
       </c>
       <c r="AZ52" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BA52" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BB52">
         <v>50.2</v>
@@ -20623,7 +20611,7 @@
         <v>1.157</v>
       </c>
       <c r="CD52" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="CE52">
         <v>1694</v>
@@ -20706,22 +20694,22 @@
         <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F53" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G53" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J53">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K53">
         <v>10.5</v>
@@ -20751,13 +20739,13 @@
         <v>75</v>
       </c>
       <c r="T53" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U53" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V53" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W53">
         <v>0.25</v>
@@ -20847,10 +20835,10 @@
         <v>129.2</v>
       </c>
       <c r="AZ53" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BA53" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BB53">
         <v>59.4</v>
@@ -20937,7 +20925,7 @@
         <v>1.1603</v>
       </c>
       <c r="CD53" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE53">
         <v>1592</v>
@@ -21020,25 +21008,25 @@
         <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F54" t="s">
         <v>116</v>
       </c>
       <c r="G54" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I54" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J54">
-        <v>469.8</v>
+        <v>471.5</v>
       </c>
       <c r="K54">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -21050,7 +21038,7 @@
         <v>1.5</v>
       </c>
       <c r="O54">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="P54">
         <v>57.9</v>
@@ -21065,13 +21053,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
+        <v>362</v>
+      </c>
+      <c r="U54" t="s">
+        <v>365</v>
+      </c>
+      <c r="V54" t="s">
         <v>366</v>
-      </c>
-      <c r="U54" t="s">
-        <v>369</v>
-      </c>
-      <c r="V54" t="s">
-        <v>370</v>
       </c>
       <c r="W54">
         <v>0.1667</v>
@@ -21161,10 +21149,10 @@
         <v>287.6</v>
       </c>
       <c r="AZ54" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BA54" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BB54">
         <v>56.3</v>
@@ -21251,7 +21239,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD54" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE54">
         <v>858</v>
@@ -21334,25 +21322,25 @@
         <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F55" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G55" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I55" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J55">
-        <v>469.8</v>
+        <v>471.5</v>
       </c>
       <c r="K55">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -21364,7 +21352,7 @@
         <v>6.17</v>
       </c>
       <c r="O55">
-        <v>2.18</v>
+        <v>0.88</v>
       </c>
       <c r="P55">
         <v>50.2</v>
@@ -21379,22 +21367,22 @@
         <v>56.2</v>
       </c>
       <c r="T55" t="s">
+        <v>362</v>
+      </c>
+      <c r="U55" t="s">
         <v>366</v>
       </c>
-      <c r="U55" t="s">
-        <v>370</v>
-      </c>
       <c r="V55" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W55">
         <v>0.1667</v>
       </c>
       <c r="X55">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
       <c r="Y55">
-        <v>67.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Z55">
         <v>52.6</v>
@@ -21436,7 +21424,7 @@
         <v>93.3</v>
       </c>
       <c r="AM55">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AN55">
         <v>0</v>
@@ -21469,16 +21457,16 @@
         <v>0</v>
       </c>
       <c r="AX55" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AY55">
         <v>58.2</v>
       </c>
       <c r="AZ55" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BA55" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="BB55">
         <v>57.3</v>
@@ -21565,7 +21553,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD55" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE55">
         <v>858</v>
@@ -21648,25 +21636,25 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F56" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G56" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I56" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J56">
-        <v>469.8</v>
+        <v>471.5</v>
       </c>
       <c r="K56">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -21678,7 +21666,7 @@
         <v>2.94</v>
       </c>
       <c r="O56">
-        <v>5.59</v>
+        <v>6.17</v>
       </c>
       <c r="P56">
         <v>58.6</v>
@@ -21693,22 +21681,22 @@
         <v>75</v>
       </c>
       <c r="T56" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U56" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V56" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W56">
         <v>0.1667</v>
       </c>
       <c r="X56">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="Y56">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z56">
         <v>53</v>
@@ -21750,7 +21738,7 @@
         <v>95.7</v>
       </c>
       <c r="AM56">
-        <v>8.4</v>
+        <v>10.1</v>
       </c>
       <c r="AN56">
         <v>0.001</v>
@@ -21783,16 +21771,16 @@
         <v>0</v>
       </c>
       <c r="AX56" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AY56">
         <v>329.5</v>
       </c>
       <c r="AZ56" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="BA56" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="BB56">
         <v>40.1</v>
@@ -21879,7 +21867,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD56" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE56">
         <v>858</v>
@@ -21962,25 +21950,25 @@
         <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F57" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G57" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="H57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I57" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J57">
-        <v>469.8</v>
+        <v>471.5</v>
       </c>
       <c r="K57">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -21992,7 +21980,7 @@
         <v>1.61</v>
       </c>
       <c r="O57">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="P57">
         <v>65</v>
@@ -22007,22 +21995,22 @@
         <v>56.2</v>
       </c>
       <c r="T57" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U57" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V57" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W57">
         <v>0.1667</v>
       </c>
       <c r="X57">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Y57">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z57">
         <v>53.2</v>
@@ -22064,7 +22052,7 @@
         <v>91.3</v>
       </c>
       <c r="AM57">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AN57">
         <v>0</v>
@@ -22097,16 +22085,16 @@
         <v>0</v>
       </c>
       <c r="AX57" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AY57">
         <v>8</v>
       </c>
       <c r="AZ57" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="BA57" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="BB57">
         <v>43</v>
@@ -22193,7 +22181,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD57" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE57">
         <v>858</v>
@@ -22244,7 +22232,7 @@
         <v>191</v>
       </c>
       <c r="CU57">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="CV57" t="s">
         <v>190</v>
@@ -22276,22 +22264,22 @@
         <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F58" t="s">
         <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H58" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I58" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J58">
-        <v>476.4</v>
+        <v>478.1</v>
       </c>
       <c r="K58">
         <v>10.1</v>
@@ -22321,13 +22309,13 @@
         <v>100</v>
       </c>
       <c r="T58" t="s">
+        <v>362</v>
+      </c>
+      <c r="U58" t="s">
         <v>366</v>
       </c>
-      <c r="U58" t="s">
-        <v>370</v>
-      </c>
       <c r="V58" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="W58">
         <v>0.8333</v>
@@ -22417,10 +22405,10 @@
         <v>17.6</v>
       </c>
       <c r="AZ58" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA58" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB58">
         <v>91.90000000000001</v>
@@ -22507,7 +22495,7 @@
         <v>1.1759</v>
       </c>
       <c r="CD58" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE58">
         <v>1242</v>
@@ -22590,22 +22578,22 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F59" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G59" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H59" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I59" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J59">
-        <v>476.4</v>
+        <v>478.1</v>
       </c>
       <c r="K59">
         <v>11.1</v>
@@ -22635,13 +22623,13 @@
         <v>100</v>
       </c>
       <c r="T59" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U59" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="V59" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="W59">
         <v>0.8333</v>
@@ -22725,16 +22713,16 @@
         <v>5.8</v>
       </c>
       <c r="AX59" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AY59">
         <v>35.1</v>
       </c>
       <c r="AZ59" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BA59" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BB59">
         <v>88.59999999999999</v>
@@ -22821,7 +22809,7 @@
         <v>1.1853</v>
       </c>
       <c r="CD59" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE59">
         <v>967</v>
@@ -22904,22 +22892,22 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F60" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G60" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I60" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J60">
-        <v>476.4</v>
+        <v>478.1</v>
       </c>
       <c r="K60">
         <v>12.1</v>
@@ -22949,13 +22937,13 @@
         <v>81.2</v>
       </c>
       <c r="T60" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U60" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="V60" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="W60">
         <v>0.8333</v>
@@ -23039,16 +23027,16 @@
         <v>6.3</v>
       </c>
       <c r="AX60" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AY60">
         <v>44</v>
       </c>
       <c r="AZ60" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BA60" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BB60">
         <v>79.59999999999999</v>
@@ -23135,7 +23123,7 @@
         <v>1.1937</v>
       </c>
       <c r="CD60" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE60">
         <v>721</v>
@@ -23218,22 +23206,22 @@
         <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F61" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G61" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H61" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I61" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J61">
-        <v>476.4</v>
+        <v>478.1</v>
       </c>
       <c r="K61">
         <v>13.1</v>
@@ -23263,13 +23251,13 @@
         <v>81.2</v>
       </c>
       <c r="T61" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="U61" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="V61" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="W61">
         <v>0.8333</v>
@@ -23353,16 +23341,16 @@
         <v>6.6</v>
       </c>
       <c r="AX61" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AY61">
         <v>48.6</v>
       </c>
       <c r="AZ61" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BA61" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BB61">
         <v>69</v>
@@ -23449,7 +23437,7 @@
         <v>1.2007</v>
       </c>
       <c r="CD61" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="CE61">
         <v>518</v>
@@ -23729,7 +23717,7 @@
         <v>163</v>
       </c>
       <c r="G4">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -23782,7 +23770,7 @@
         <v>163</v>
       </c>
       <c r="G5">
-        <v>94.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -24259,7 +24247,7 @@
         <v>165</v>
       </c>
       <c r="G14">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -24312,7 +24300,7 @@
         <v>165</v>
       </c>
       <c r="G15">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H15">
         <v>0</v>
